--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,12 +107,6 @@
       <name val="Arial"/>
       <color rgb="00008000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -219,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -228,7 +222,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -289,28 +283,25 @@
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -677,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -846,38 +837,30 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
+          <t>Os incentivos são simples: entram pelo valor apurado, sem dobrar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Em julho/2026 a comissão foi lançada por média. Com a comissão dobrada a partir de agosto, a empresa vai reduzir nas premiações a diferença.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>UILLIAN: não recebe comissão sobre vendas (mesmo critério de julho/2026) — a rubrica fica zerada e o apurado dele aparece só na aba BASE.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -889,7 +872,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -901,7 +884,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -913,7 +896,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Conferir como as comissões de julho foram efetivamente pagas: a planilha traz o valor simples e o pagamento da loja é em dobro.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -925,7 +908,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Confirmar se o dobro vale só para a comissão. Os incentivos estão lançados pelo valor apurado, sem dobrar.</t>
+          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
         </is>
       </c>
     </row>
@@ -937,7 +920,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INIURLE: em julho as horas extras foram lançadas como R$ 442,09, exatamente o mesmo valor do EDEY na loja Arraial — conferir se não houve cópia de célula.</t>
+          <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada, para compensar o aumento da comissão dobrada.</t>
         </is>
       </c>
     </row>
@@ -949,37 +932,41 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>INIURLE: em julho as horas extras foram lançadas como R$ 442,09, exatamente o mesmo valor do EDEY na loja Arraial — conferir se não houve cópia de célula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
           <t>UILLIAN também registra vendas no relatório da loja Centro — conferir se alguma comissão deve ser rateada entre as lojas.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -987,7 +974,7 @@
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -995,7 +982,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +990,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1019,6 +1006,14 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
@@ -1026,14 +1021,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2016,18 +2011,18 @@
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="20">
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="31">
         <f>SUM(B15:F15)</f>
         <v/>
       </c>
       <c r="H15" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER conforme a tabela de metas da loja (aba METAS da planilha original).</t>
+          <t>PREENCHER conforme a tabela de metas da loja (aba METAS da planilha original). Lançar já com a redução combinada para compensar o aumento da comissão dobrada.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="H19" s="32" t="inlineStr">
         <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma. NÃO está multiplicado por 2 — confirmar se o dobro vale só para a comissão.</t>
+          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3395,10 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
+    <row r="36">
       <c r="A36" s="39" t="inlineStr">
         <is>
-          <t>ATENÇÃO: as comissões desta aba estão pelo valor da planilha (R$ 850,00 do MANOEL, R$ 908,70 do VALDICK etc.), na mesma ordem de grandeza do apurado no sistema. Como o pagamento da loja é o DOBRO da comissão, o líquido revisado acima reproduz a planilha e não o valor efetivamente pago — conferir com a contabilidade como julho foi lançado.</t>
+          <t>OBSERVAÇÃO: em julho/2026 a comissão foi lançada por uma MÉDIA, e não pelo apurado do sistema. A partir de agosto/2026 a loja passa a pagar a comissão em dobro, e a empresa vai reduzir nas premiações a diferença gerada por esse aumento.</t>
         </is>
       </c>
     </row>
@@ -3415,28 +3410,28 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>1. Rubricas separadas em PROVENTOS × DESCONTOS, com subtotais próprios.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>2. Nomes de rubrica padronizados e coluna de observação com a origem de cada valor.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>3. Conferência do DSR: em julho foi usado o fator de agosto (5/26) em vez de 4/27.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>4. Linha de conferência comparando o líquido revisado com o SALDO FINAL da planilha original (tem que fechar em zero).</t>
         </is>
@@ -3535,7 +3530,7 @@
         <f>'HOLERITE AGO.26'!B6</f>
         <v/>
       </c>
-      <c r="E5" s="42" t="n"/>
+      <c r="E5" s="41" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -3557,7 +3552,7 @@
         <f>'HOLERITE AGO.26'!B7</f>
         <v/>
       </c>
-      <c r="E6" s="42" t="n"/>
+      <c r="E6" s="41" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -3579,7 +3574,7 @@
         <f>'HOLERITE AGO.26'!B8</f>
         <v/>
       </c>
-      <c r="E7" s="42" t="n"/>
+      <c r="E7" s="41" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3601,7 +3596,7 @@
         <f>'HOLERITE AGO.26'!B11</f>
         <v/>
       </c>
-      <c r="E8" s="42" t="n"/>
+      <c r="E8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3623,7 +3618,7 @@
         <f>'HOLERITE AGO.26'!B12</f>
         <v/>
       </c>
-      <c r="E9" s="42" t="n"/>
+      <c r="E9" s="41" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3645,7 +3640,7 @@
         <f>'HOLERITE AGO.26'!B13</f>
         <v/>
       </c>
-      <c r="E10" s="42" t="n"/>
+      <c r="E10" s="41" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3667,7 +3662,7 @@
         <f>'HOLERITE AGO.26'!B14</f>
         <v/>
       </c>
-      <c r="E11" s="42" t="n"/>
+      <c r="E11" s="41" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3689,7 +3684,7 @@
         <f>'HOLERITE AGO.26'!B15</f>
         <v/>
       </c>
-      <c r="E12" s="42" t="n"/>
+      <c r="E12" s="41" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
@@ -3711,7 +3706,7 @@
         <f>'HOLERITE AGO.26'!B16</f>
         <v/>
       </c>
-      <c r="E13" s="42" t="n"/>
+      <c r="E13" s="41" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
@@ -3733,7 +3728,7 @@
         <f>'HOLERITE AGO.26'!B17</f>
         <v/>
       </c>
-      <c r="E14" s="42" t="n"/>
+      <c r="E14" s="41" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
@@ -3755,7 +3750,7 @@
         <f>'HOLERITE AGO.26'!B18</f>
         <v/>
       </c>
-      <c r="E15" s="42" t="n"/>
+      <c r="E15" s="41" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
@@ -3777,7 +3772,7 @@
         <f>'HOLERITE AGO.26'!B19</f>
         <v/>
       </c>
-      <c r="E16" s="42" t="n"/>
+      <c r="E16" s="41" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
@@ -3799,7 +3794,7 @@
         <f>'HOLERITE AGO.26'!B20</f>
         <v/>
       </c>
-      <c r="E17" s="42" t="n"/>
+      <c r="E17" s="41" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -3821,25 +3816,25 @@
         <f>'HOLERITE AGO.26'!B21</f>
         <v/>
       </c>
-      <c r="E18" s="42" t="n"/>
+      <c r="E18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="43">
         <f>'HOLERITE AGO.26'!B22</f>
         <v/>
       </c>
@@ -3865,7 +3860,7 @@
         <f>'HOLERITE AGO.26'!B24</f>
         <v/>
       </c>
-      <c r="E20" s="42" t="n"/>
+      <c r="E20" s="41" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
@@ -3887,7 +3882,7 @@
         <f>'HOLERITE AGO.26'!B25</f>
         <v/>
       </c>
-      <c r="E21" s="42" t="n"/>
+      <c r="E21" s="41" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
@@ -3909,7 +3904,7 @@
         <f>'HOLERITE AGO.26'!B26</f>
         <v/>
       </c>
-      <c r="E22" s="42" t="n"/>
+      <c r="E22" s="41" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
@@ -3931,7 +3926,7 @@
         <f>'HOLERITE AGO.26'!B27</f>
         <v/>
       </c>
-      <c r="E23" s="42" t="n"/>
+      <c r="E23" s="41" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
@@ -3953,7 +3948,7 @@
         <f>'HOLERITE AGO.26'!B28</f>
         <v/>
       </c>
-      <c r="E24" s="42" t="n"/>
+      <c r="E24" s="41" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
@@ -3975,7 +3970,7 @@
         <f>'HOLERITE AGO.26'!B29</f>
         <v/>
       </c>
-      <c r="E25" s="42" t="n"/>
+      <c r="E25" s="41" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
@@ -3997,51 +3992,51 @@
         <f>'HOLERITE AGO.26'!B30</f>
         <v/>
       </c>
-      <c r="E26" s="42" t="n"/>
+      <c r="E26" s="41" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="43">
         <f>'HOLERITE AGO.26'!B31</f>
         <v/>
       </c>
       <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="A28" s="44" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="46">
         <f>'HOLERITE AGO.26'!B33</f>
         <v/>
       </c>
-      <c r="E28" s="48" t="n"/>
+      <c r="E28" s="47" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
@@ -4063,7 +4058,7 @@
         <f>'HOLERITE AGO.26'!C6</f>
         <v/>
       </c>
-      <c r="E30" s="42" t="n"/>
+      <c r="E30" s="41" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
@@ -4085,7 +4080,7 @@
         <f>'HOLERITE AGO.26'!C7</f>
         <v/>
       </c>
-      <c r="E31" s="42" t="n"/>
+      <c r="E31" s="41" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
@@ -4107,7 +4102,7 @@
         <f>'HOLERITE AGO.26'!C8</f>
         <v/>
       </c>
-      <c r="E32" s="42" t="n"/>
+      <c r="E32" s="41" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
@@ -4129,7 +4124,7 @@
         <f>'HOLERITE AGO.26'!C11</f>
         <v/>
       </c>
-      <c r="E33" s="42" t="n"/>
+      <c r="E33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
@@ -4151,7 +4146,7 @@
         <f>'HOLERITE AGO.26'!C12</f>
         <v/>
       </c>
-      <c r="E34" s="42" t="n"/>
+      <c r="E34" s="41" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
@@ -4173,7 +4168,7 @@
         <f>'HOLERITE AGO.26'!C13</f>
         <v/>
       </c>
-      <c r="E35" s="42" t="n"/>
+      <c r="E35" s="41" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
@@ -4195,7 +4190,7 @@
         <f>'HOLERITE AGO.26'!C14</f>
         <v/>
       </c>
-      <c r="E36" s="42" t="n"/>
+      <c r="E36" s="41" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
@@ -4217,7 +4212,7 @@
         <f>'HOLERITE AGO.26'!C15</f>
         <v/>
       </c>
-      <c r="E37" s="42" t="n"/>
+      <c r="E37" s="41" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
@@ -4239,7 +4234,7 @@
         <f>'HOLERITE AGO.26'!C16</f>
         <v/>
       </c>
-      <c r="E38" s="42" t="n"/>
+      <c r="E38" s="41" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
@@ -4261,7 +4256,7 @@
         <f>'HOLERITE AGO.26'!C17</f>
         <v/>
       </c>
-      <c r="E39" s="42" t="n"/>
+      <c r="E39" s="41" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
@@ -4283,7 +4278,7 @@
         <f>'HOLERITE AGO.26'!C18</f>
         <v/>
       </c>
-      <c r="E40" s="42" t="n"/>
+      <c r="E40" s="41" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
@@ -4305,7 +4300,7 @@
         <f>'HOLERITE AGO.26'!C19</f>
         <v/>
       </c>
-      <c r="E41" s="42" t="n"/>
+      <c r="E41" s="41" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
@@ -4327,7 +4322,7 @@
         <f>'HOLERITE AGO.26'!C20</f>
         <v/>
       </c>
-      <c r="E42" s="42" t="n"/>
+      <c r="E42" s="41" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
@@ -4349,25 +4344,25 @@
         <f>'HOLERITE AGO.26'!C21</f>
         <v/>
       </c>
-      <c r="E43" s="42" t="n"/>
+      <c r="E43" s="41" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B44" s="43" t="inlineStr">
+      <c r="B44" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="C44" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="43">
         <f>'HOLERITE AGO.26'!C22</f>
         <v/>
       </c>
@@ -4393,7 +4388,7 @@
         <f>'HOLERITE AGO.26'!C24</f>
         <v/>
       </c>
-      <c r="E45" s="42" t="n"/>
+      <c r="E45" s="41" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
@@ -4415,7 +4410,7 @@
         <f>'HOLERITE AGO.26'!C25</f>
         <v/>
       </c>
-      <c r="E46" s="42" t="n"/>
+      <c r="E46" s="41" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
@@ -4437,7 +4432,7 @@
         <f>'HOLERITE AGO.26'!C26</f>
         <v/>
       </c>
-      <c r="E47" s="42" t="n"/>
+      <c r="E47" s="41" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
@@ -4459,7 +4454,7 @@
         <f>'HOLERITE AGO.26'!C27</f>
         <v/>
       </c>
-      <c r="E48" s="42" t="n"/>
+      <c r="E48" s="41" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
@@ -4481,7 +4476,7 @@
         <f>'HOLERITE AGO.26'!C28</f>
         <v/>
       </c>
-      <c r="E49" s="42" t="n"/>
+      <c r="E49" s="41" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
@@ -4503,7 +4498,7 @@
         <f>'HOLERITE AGO.26'!C29</f>
         <v/>
       </c>
-      <c r="E50" s="42" t="n"/>
+      <c r="E50" s="41" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
@@ -4525,51 +4520,51 @@
         <f>'HOLERITE AGO.26'!C30</f>
         <v/>
       </c>
-      <c r="E51" s="42" t="n"/>
+      <c r="E51" s="41" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B52" s="43" t="inlineStr">
+      <c r="B52" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C52" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D52" s="44">
+      <c r="D52" s="43">
         <f>'HOLERITE AGO.26'!C31</f>
         <v/>
       </c>
       <c r="E52" s="18" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="45" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B53" s="46" t="inlineStr">
+      <c r="B53" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C53" s="46" t="inlineStr">
+      <c r="C53" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D53" s="47">
+      <c r="D53" s="46">
         <f>'HOLERITE AGO.26'!C33</f>
         <v/>
       </c>
-      <c r="E53" s="48" t="n"/>
+      <c r="E53" s="47" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
@@ -4591,7 +4586,7 @@
         <f>'HOLERITE AGO.26'!D6</f>
         <v/>
       </c>
-      <c r="E55" s="42" t="n"/>
+      <c r="E55" s="41" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
@@ -4613,7 +4608,7 @@
         <f>'HOLERITE AGO.26'!D7</f>
         <v/>
       </c>
-      <c r="E56" s="42" t="n"/>
+      <c r="E56" s="41" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
@@ -4635,7 +4630,7 @@
         <f>'HOLERITE AGO.26'!D8</f>
         <v/>
       </c>
-      <c r="E57" s="42" t="n"/>
+      <c r="E57" s="41" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
@@ -4657,7 +4652,7 @@
         <f>'HOLERITE AGO.26'!D11</f>
         <v/>
       </c>
-      <c r="E58" s="42" t="n"/>
+      <c r="E58" s="41" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
@@ -4679,7 +4674,7 @@
         <f>'HOLERITE AGO.26'!D12</f>
         <v/>
       </c>
-      <c r="E59" s="42" t="n"/>
+      <c r="E59" s="41" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
@@ -4701,7 +4696,7 @@
         <f>'HOLERITE AGO.26'!D13</f>
         <v/>
       </c>
-      <c r="E60" s="42" t="n"/>
+      <c r="E60" s="41" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
@@ -4723,7 +4718,7 @@
         <f>'HOLERITE AGO.26'!D14</f>
         <v/>
       </c>
-      <c r="E61" s="42" t="n"/>
+      <c r="E61" s="41" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
@@ -4745,7 +4740,7 @@
         <f>'HOLERITE AGO.26'!D15</f>
         <v/>
       </c>
-      <c r="E62" s="42" t="n"/>
+      <c r="E62" s="41" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
@@ -4767,7 +4762,7 @@
         <f>'HOLERITE AGO.26'!D16</f>
         <v/>
       </c>
-      <c r="E63" s="42" t="n"/>
+      <c r="E63" s="41" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
@@ -4789,7 +4784,7 @@
         <f>'HOLERITE AGO.26'!D17</f>
         <v/>
       </c>
-      <c r="E64" s="42" t="n"/>
+      <c r="E64" s="41" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
@@ -4811,7 +4806,7 @@
         <f>'HOLERITE AGO.26'!D18</f>
         <v/>
       </c>
-      <c r="E65" s="42" t="n"/>
+      <c r="E65" s="41" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
@@ -4833,7 +4828,7 @@
         <f>'HOLERITE AGO.26'!D19</f>
         <v/>
       </c>
-      <c r="E66" s="42" t="n"/>
+      <c r="E66" s="41" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
@@ -4855,7 +4850,7 @@
         <f>'HOLERITE AGO.26'!D20</f>
         <v/>
       </c>
-      <c r="E67" s="42" t="n"/>
+      <c r="E67" s="41" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
@@ -4877,25 +4872,25 @@
         <f>'HOLERITE AGO.26'!D21</f>
         <v/>
       </c>
-      <c r="E68" s="42" t="n"/>
+      <c r="E68" s="41" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="43" t="inlineStr">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B69" s="43" t="inlineStr">
+      <c r="B69" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C69" s="43" t="inlineStr">
+      <c r="C69" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D69" s="44">
+      <c r="D69" s="43">
         <f>'HOLERITE AGO.26'!D22</f>
         <v/>
       </c>
@@ -4921,7 +4916,7 @@
         <f>'HOLERITE AGO.26'!D24</f>
         <v/>
       </c>
-      <c r="E70" s="42" t="n"/>
+      <c r="E70" s="41" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
@@ -4943,7 +4938,7 @@
         <f>'HOLERITE AGO.26'!D25</f>
         <v/>
       </c>
-      <c r="E71" s="42" t="n"/>
+      <c r="E71" s="41" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
@@ -4965,7 +4960,7 @@
         <f>'HOLERITE AGO.26'!D26</f>
         <v/>
       </c>
-      <c r="E72" s="42" t="n"/>
+      <c r="E72" s="41" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
@@ -4987,7 +4982,7 @@
         <f>'HOLERITE AGO.26'!D27</f>
         <v/>
       </c>
-      <c r="E73" s="42" t="n"/>
+      <c r="E73" s="41" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
@@ -5009,7 +5004,7 @@
         <f>'HOLERITE AGO.26'!D28</f>
         <v/>
       </c>
-      <c r="E74" s="42" t="n"/>
+      <c r="E74" s="41" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
@@ -5031,7 +5026,7 @@
         <f>'HOLERITE AGO.26'!D29</f>
         <v/>
       </c>
-      <c r="E75" s="42" t="n"/>
+      <c r="E75" s="41" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
@@ -5053,51 +5048,51 @@
         <f>'HOLERITE AGO.26'!D30</f>
         <v/>
       </c>
-      <c r="E76" s="42" t="n"/>
+      <c r="E76" s="41" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="43" t="inlineStr">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B77" s="43" t="inlineStr">
+      <c r="B77" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C77" s="43" t="inlineStr">
+      <c r="C77" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D77" s="44">
+      <c r="D77" s="43">
         <f>'HOLERITE AGO.26'!D31</f>
         <v/>
       </c>
       <c r="E77" s="18" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="45" t="inlineStr">
+      <c r="A78" s="44" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B78" s="46" t="inlineStr">
+      <c r="B78" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C78" s="46" t="inlineStr">
+      <c r="C78" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D78" s="47">
+      <c r="D78" s="46">
         <f>'HOLERITE AGO.26'!D33</f>
         <v/>
       </c>
-      <c r="E78" s="48" t="n"/>
+      <c r="E78" s="47" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
@@ -5119,7 +5114,7 @@
         <f>'HOLERITE AGO.26'!E6</f>
         <v/>
       </c>
-      <c r="E80" s="42" t="n"/>
+      <c r="E80" s="41" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
@@ -5141,7 +5136,7 @@
         <f>'HOLERITE AGO.26'!E7</f>
         <v/>
       </c>
-      <c r="E81" s="42" t="n"/>
+      <c r="E81" s="41" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
@@ -5163,7 +5158,7 @@
         <f>'HOLERITE AGO.26'!E8</f>
         <v/>
       </c>
-      <c r="E82" s="42" t="n"/>
+      <c r="E82" s="41" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
@@ -5185,7 +5180,7 @@
         <f>'HOLERITE AGO.26'!E11</f>
         <v/>
       </c>
-      <c r="E83" s="42" t="n"/>
+      <c r="E83" s="41" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
@@ -5207,7 +5202,7 @@
         <f>'HOLERITE AGO.26'!E12</f>
         <v/>
       </c>
-      <c r="E84" s="42" t="n"/>
+      <c r="E84" s="41" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="29" t="inlineStr">
@@ -5229,7 +5224,7 @@
         <f>'HOLERITE AGO.26'!E13</f>
         <v/>
       </c>
-      <c r="E85" s="42" t="n"/>
+      <c r="E85" s="41" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
@@ -5251,7 +5246,7 @@
         <f>'HOLERITE AGO.26'!E14</f>
         <v/>
       </c>
-      <c r="E86" s="42" t="n"/>
+      <c r="E86" s="41" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
@@ -5273,7 +5268,7 @@
         <f>'HOLERITE AGO.26'!E15</f>
         <v/>
       </c>
-      <c r="E87" s="42" t="n"/>
+      <c r="E87" s="41" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
@@ -5295,7 +5290,7 @@
         <f>'HOLERITE AGO.26'!E16</f>
         <v/>
       </c>
-      <c r="E88" s="42" t="n"/>
+      <c r="E88" s="41" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
@@ -5317,7 +5312,7 @@
         <f>'HOLERITE AGO.26'!E17</f>
         <v/>
       </c>
-      <c r="E89" s="42" t="n"/>
+      <c r="E89" s="41" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="29" t="inlineStr">
@@ -5339,7 +5334,7 @@
         <f>'HOLERITE AGO.26'!E18</f>
         <v/>
       </c>
-      <c r="E90" s="42" t="n"/>
+      <c r="E90" s="41" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="29" t="inlineStr">
@@ -5361,7 +5356,7 @@
         <f>'HOLERITE AGO.26'!E19</f>
         <v/>
       </c>
-      <c r="E91" s="42" t="n"/>
+      <c r="E91" s="41" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="29" t="inlineStr">
@@ -5383,7 +5378,7 @@
         <f>'HOLERITE AGO.26'!E20</f>
         <v/>
       </c>
-      <c r="E92" s="42" t="n"/>
+      <c r="E92" s="41" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
@@ -5405,25 +5400,25 @@
         <f>'HOLERITE AGO.26'!E21</f>
         <v/>
       </c>
-      <c r="E93" s="42" t="n"/>
+      <c r="E93" s="41" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="43" t="inlineStr">
+      <c r="A94" s="42" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B94" s="43" t="inlineStr">
+      <c r="B94" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C94" s="43" t="inlineStr">
+      <c r="C94" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D94" s="44">
+      <c r="D94" s="43">
         <f>'HOLERITE AGO.26'!E22</f>
         <v/>
       </c>
@@ -5449,7 +5444,7 @@
         <f>'HOLERITE AGO.26'!E24</f>
         <v/>
       </c>
-      <c r="E95" s="42" t="n"/>
+      <c r="E95" s="41" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="29" t="inlineStr">
@@ -5471,7 +5466,7 @@
         <f>'HOLERITE AGO.26'!E25</f>
         <v/>
       </c>
-      <c r="E96" s="42" t="n"/>
+      <c r="E96" s="41" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="29" t="inlineStr">
@@ -5493,7 +5488,7 @@
         <f>'HOLERITE AGO.26'!E26</f>
         <v/>
       </c>
-      <c r="E97" s="42" t="n"/>
+      <c r="E97" s="41" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="29" t="inlineStr">
@@ -5515,7 +5510,7 @@
         <f>'HOLERITE AGO.26'!E27</f>
         <v/>
       </c>
-      <c r="E98" s="42" t="n"/>
+      <c r="E98" s="41" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="29" t="inlineStr">
@@ -5537,7 +5532,7 @@
         <f>'HOLERITE AGO.26'!E28</f>
         <v/>
       </c>
-      <c r="E99" s="42" t="n"/>
+      <c r="E99" s="41" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="29" t="inlineStr">
@@ -5559,7 +5554,7 @@
         <f>'HOLERITE AGO.26'!E29</f>
         <v/>
       </c>
-      <c r="E100" s="42" t="n"/>
+      <c r="E100" s="41" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="29" t="inlineStr">
@@ -5581,51 +5576,51 @@
         <f>'HOLERITE AGO.26'!E30</f>
         <v/>
       </c>
-      <c r="E101" s="42" t="n"/>
+      <c r="E101" s="41" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="43" t="inlineStr">
+      <c r="A102" s="42" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B102" s="43" t="inlineStr">
+      <c r="B102" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C102" s="43" t="inlineStr">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="44">
+      <c r="D102" s="43">
         <f>'HOLERITE AGO.26'!E31</f>
         <v/>
       </c>
       <c r="E102" s="18" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="45" t="inlineStr">
+      <c r="A103" s="44" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B103" s="46" t="inlineStr">
+      <c r="B103" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C103" s="46" t="inlineStr">
+      <c r="C103" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D103" s="47">
+      <c r="D103" s="46">
         <f>'HOLERITE AGO.26'!E33</f>
         <v/>
       </c>
-      <c r="E103" s="48" t="n"/>
+      <c r="E103" s="47" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="29" t="inlineStr">
@@ -5647,7 +5642,7 @@
         <f>'HOLERITE AGO.26'!F6</f>
         <v/>
       </c>
-      <c r="E105" s="42" t="n"/>
+      <c r="E105" s="41" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="29" t="inlineStr">
@@ -5669,7 +5664,7 @@
         <f>'HOLERITE AGO.26'!F7</f>
         <v/>
       </c>
-      <c r="E106" s="42" t="n"/>
+      <c r="E106" s="41" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="29" t="inlineStr">
@@ -5691,7 +5686,7 @@
         <f>'HOLERITE AGO.26'!F8</f>
         <v/>
       </c>
-      <c r="E107" s="42" t="n"/>
+      <c r="E107" s="41" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="29" t="inlineStr">
@@ -5713,7 +5708,7 @@
         <f>'HOLERITE AGO.26'!F11</f>
         <v/>
       </c>
-      <c r="E108" s="42" t="n"/>
+      <c r="E108" s="41" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="29" t="inlineStr">
@@ -5735,7 +5730,7 @@
         <f>'HOLERITE AGO.26'!F12</f>
         <v/>
       </c>
-      <c r="E109" s="42" t="n"/>
+      <c r="E109" s="41" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
@@ -5757,7 +5752,7 @@
         <f>'HOLERITE AGO.26'!F13</f>
         <v/>
       </c>
-      <c r="E110" s="42" t="n"/>
+      <c r="E110" s="41" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="29" t="inlineStr">
@@ -5779,7 +5774,7 @@
         <f>'HOLERITE AGO.26'!F14</f>
         <v/>
       </c>
-      <c r="E111" s="42" t="n"/>
+      <c r="E111" s="41" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
@@ -5801,7 +5796,7 @@
         <f>'HOLERITE AGO.26'!F15</f>
         <v/>
       </c>
-      <c r="E112" s="42" t="n"/>
+      <c r="E112" s="41" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
@@ -5823,7 +5818,7 @@
         <f>'HOLERITE AGO.26'!F16</f>
         <v/>
       </c>
-      <c r="E113" s="42" t="n"/>
+      <c r="E113" s="41" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="29" t="inlineStr">
@@ -5845,7 +5840,7 @@
         <f>'HOLERITE AGO.26'!F17</f>
         <v/>
       </c>
-      <c r="E114" s="42" t="n"/>
+      <c r="E114" s="41" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="29" t="inlineStr">
@@ -5867,7 +5862,7 @@
         <f>'HOLERITE AGO.26'!F18</f>
         <v/>
       </c>
-      <c r="E115" s="42" t="n"/>
+      <c r="E115" s="41" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="29" t="inlineStr">
@@ -5889,7 +5884,7 @@
         <f>'HOLERITE AGO.26'!F19</f>
         <v/>
       </c>
-      <c r="E116" s="42" t="n"/>
+      <c r="E116" s="41" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="29" t="inlineStr">
@@ -5911,7 +5906,7 @@
         <f>'HOLERITE AGO.26'!F20</f>
         <v/>
       </c>
-      <c r="E117" s="42" t="n"/>
+      <c r="E117" s="41" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="29" t="inlineStr">
@@ -5933,25 +5928,25 @@
         <f>'HOLERITE AGO.26'!F21</f>
         <v/>
       </c>
-      <c r="E118" s="42" t="n"/>
+      <c r="E118" s="41" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="43" t="inlineStr">
+      <c r="A119" s="42" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B119" s="43" t="inlineStr">
+      <c r="B119" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C119" s="43" t="inlineStr">
+      <c r="C119" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D119" s="44">
+      <c r="D119" s="43">
         <f>'HOLERITE AGO.26'!F22</f>
         <v/>
       </c>
@@ -5977,7 +5972,7 @@
         <f>'HOLERITE AGO.26'!F24</f>
         <v/>
       </c>
-      <c r="E120" s="42" t="n"/>
+      <c r="E120" s="41" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="29" t="inlineStr">
@@ -5999,7 +5994,7 @@
         <f>'HOLERITE AGO.26'!F25</f>
         <v/>
       </c>
-      <c r="E121" s="42" t="n"/>
+      <c r="E121" s="41" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="29" t="inlineStr">
@@ -6021,7 +6016,7 @@
         <f>'HOLERITE AGO.26'!F26</f>
         <v/>
       </c>
-      <c r="E122" s="42" t="n"/>
+      <c r="E122" s="41" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="29" t="inlineStr">
@@ -6043,7 +6038,7 @@
         <f>'HOLERITE AGO.26'!F27</f>
         <v/>
       </c>
-      <c r="E123" s="42" t="n"/>
+      <c r="E123" s="41" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="29" t="inlineStr">
@@ -6065,7 +6060,7 @@
         <f>'HOLERITE AGO.26'!F28</f>
         <v/>
       </c>
-      <c r="E124" s="42" t="n"/>
+      <c r="E124" s="41" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="29" t="inlineStr">
@@ -6087,7 +6082,7 @@
         <f>'HOLERITE AGO.26'!F29</f>
         <v/>
       </c>
-      <c r="E125" s="42" t="n"/>
+      <c r="E125" s="41" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="29" t="inlineStr">
@@ -6109,51 +6104,51 @@
         <f>'HOLERITE AGO.26'!F30</f>
         <v/>
       </c>
-      <c r="E126" s="42" t="n"/>
+      <c r="E126" s="41" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="43" t="inlineStr">
+      <c r="A127" s="42" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B127" s="43" t="inlineStr">
+      <c r="B127" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C127" s="43" t="inlineStr">
+      <c r="C127" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D127" s="44">
+      <c r="D127" s="43">
         <f>'HOLERITE AGO.26'!F31</f>
         <v/>
       </c>
       <c r="E127" s="18" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="45" t="inlineStr">
+      <c r="A128" s="44" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B128" s="46" t="inlineStr">
+      <c r="B128" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C128" s="46" t="inlineStr">
+      <c r="C128" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D128" s="47">
+      <c r="D128" s="46">
         <f>'HOLERITE AGO.26'!F33</f>
         <v/>
       </c>
-      <c r="E128" s="48" t="n"/>
+      <c r="E128" s="47" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E128"/>
@@ -6195,12 +6190,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Escolha o colaborador:</t>
         </is>
       </c>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
@@ -6380,7 +6375,7 @@
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="43">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6477,7 +6472,7 @@
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="43">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6492,18 +6487,18 @@
       <c r="D31" s="28" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="51" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/09/2026</t>
         </is>
       </c>
-      <c r="C32" s="52">
+      <c r="C32" s="51">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="53" t="inlineStr">
+      <c r="B34" s="52" t="inlineStr">
         <is>
           <t>Vendas do colaborador no mês (InovaFarma):</t>
         </is>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -14,6 +14,7 @@
     <sheet name="JULHO.26 REVISADO" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="GANHOS DO COLABORADOR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PONTO AGO.26" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$9</definedName>
@@ -21,6 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -277,8 +279,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -303,6 +305,8 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -872,7 +876,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
+          <t>Horas extras, adicional noturno e feriados trabalhados de agosto — lançar na aba PONTO AGO.26.</t>
         </is>
       </c>
     </row>
@@ -932,41 +936,37 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INIURLE: em julho as horas extras foram lançadas como R$ 442,09, exatamente o mesmo valor do EDEY na loja Arraial — conferir se não houve cópia de célula.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
           <t>UILLIAN também registra vendas no relatório da loja Centro — conferir se alguma comissão deve ser rateada entre as lojas.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>PONTO AGO.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
       </c>
     </row>
@@ -1024,11 +1024,11 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1229,54 +1229,114 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Multiplicador da comissão</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>2</v>
+          <t>Horas mensais (base do salário-hora)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>220</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>TRANCOSO paga o dobro do valor apurado no InovaFarma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>INSS / IRRF</t>
+          <t>Salário-hora = salário base ÷ 220.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Adicional de hora extra</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>50% sobre a hora normal (hora extra = salário-hora × 1,5).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>a calcular</t>
-        </is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+          <t>20% sobre a hora normal, nas horas entre 22h e 5h.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>Dias do mês para o salário-dia</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Salário-dia = salário base ÷ 30. Usado no feriado trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Multiplicador da comissão</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>TRANCOSO paga o dobro do valor apurado no InovaFarma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>INSS / IRRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>a calcular</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>a calcular</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Calculado pela contabilidade após dedução do INSS e dependentes.</t>
         </is>
@@ -1287,7 +1347,7 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -1801,18 +1861,33 @@
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
+      <c r="B7" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,B$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="C7" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,C$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="D7" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,D$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="E7" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,E$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="F7" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,F$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
       <c r="G7" s="20">
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
       <c r="H7" s="32" t="inlineStr">
         <is>
-          <t>Conforme apontamento do ponto.</t>
+          <t>Somado automaticamente da aba PONTO AGO.26 (apontamento de agosto/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
@@ -1822,18 +1897,33 @@
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
+      <c r="B8" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,B$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="C8" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,C$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="D8" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,D$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,E$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="F8" s="33">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,F$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
       <c r="G8" s="20">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
       <c r="H8" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER com o apurado no ponto de agosto/2026.</t>
+          <t>Somado automaticamente da aba PONTO AGO.26 (apontamento de agosto/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
@@ -1843,23 +1933,23 @@
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="34">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F6*PARÂMETROS!$B$16,2)</f>
-        <v/>
-      </c>
-      <c r="D9" s="34">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F7*PARÂMETROS!$B$16,2)</f>
-        <v/>
-      </c>
-      <c r="E9" s="34">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F8*PARÂMETROS!$B$16,2)</f>
-        <v/>
-      </c>
-      <c r="F9" s="34">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F9*PARÂMETROS!$B$16,2)</f>
+      <c r="C9" s="33">
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F6*PARÂMETROS!$B$20,2)</f>
+        <v/>
+      </c>
+      <c r="D9" s="33">
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F7*PARÂMETROS!$B$20,2)</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F8*PARÂMETROS!$B$20,2)</f>
+        <v/>
+      </c>
+      <c r="F9" s="33">
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F9*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
       <c r="G9" s="20">
@@ -1878,11 +1968,11 @@
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
       <c r="G10" s="20">
         <f>SUM(B10:F10)</f>
         <v/>
@@ -1969,11 +2059,11 @@
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
       <c r="G13" s="20">
         <f>SUM(B13:F13)</f>
         <v/>
@@ -1990,11 +2080,11 @@
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="33" t="n"/>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="34" t="n"/>
       <c r="G14" s="20">
         <f>SUM(B14:F14)</f>
         <v/>
@@ -2032,11 +2122,11 @@
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
       <c r="G16" s="20">
         <f>SUM(B16:F16)</f>
         <v/>
@@ -2053,11 +2143,11 @@
           <t>FÉRIAS (DIAS GOZADOS)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="34" t="n"/>
       <c r="G17" s="20">
         <f>SUM(B17:F17)</f>
         <v/>
@@ -2074,11 +2164,11 @@
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="33" t="n"/>
-      <c r="E18" s="33" t="n"/>
-      <c r="F18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
       <c r="G18" s="20">
         <f>SUM(B18:F18)</f>
         <v/>
@@ -2095,23 +2185,23 @@
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="33">
         <f>'BASE INOVAFARMA AGO.26'!G5</f>
         <v/>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <f>'BASE INOVAFARMA AGO.26'!G6</f>
         <v/>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <f>'BASE INOVAFARMA AGO.26'!G7</f>
         <v/>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="33">
         <f>'BASE INOVAFARMA AGO.26'!G8</f>
         <v/>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="33">
         <f>'BASE INOVAFARMA AGO.26'!G9</f>
         <v/>
       </c>
@@ -2131,23 +2221,23 @@
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="33">
         <f>'BASE INOVAFARMA AGO.26'!H5</f>
         <v/>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <f>'BASE INOVAFARMA AGO.26'!H6</f>
         <v/>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <f>'BASE INOVAFARMA AGO.26'!H7</f>
         <v/>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="33">
         <f>'BASE INOVAFARMA AGO.26'!H8</f>
         <v/>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="33">
         <f>'BASE INOVAFARMA AGO.26'!H9</f>
         <v/>
       </c>
@@ -2167,23 +2257,23 @@
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="33">
         <f>'BASE INOVAFARMA AGO.26'!I5</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <f>'BASE INOVAFARMA AGO.26'!I6</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <f>'BASE INOVAFARMA AGO.26'!I7</f>
         <v/>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="33">
         <f>'BASE INOVAFARMA AGO.26'!I8</f>
         <v/>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="33">
         <f>'BASE INOVAFARMA AGO.26'!I9</f>
         <v/>
       </c>
@@ -2253,11 +2343,11 @@
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="B24" s="33" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="33" t="n"/>
-      <c r="F24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="34" t="n"/>
       <c r="G24" s="20">
         <f>SUM(B24:F24)</f>
         <v/>
@@ -2310,11 +2400,11 @@
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="B26" s="33" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="33" t="n"/>
-      <c r="F26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="34" t="n"/>
+      <c r="D26" s="34" t="n"/>
+      <c r="E26" s="34" t="n"/>
+      <c r="F26" s="34" t="n"/>
       <c r="G26" s="20">
         <f>SUM(B26:F26)</f>
         <v/>
@@ -2331,11 +2421,11 @@
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
       <c r="G27" s="20">
         <f>SUM(B27:F27)</f>
         <v/>
@@ -2373,11 +2463,11 @@
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B29" s="33" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
-      <c r="F29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
       <c r="G29" s="20">
         <f>SUM(B29:F29)</f>
         <v/>
@@ -2394,11 +2484,11 @@
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B30" s="33" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="34" t="n"/>
       <c r="G30" s="20">
         <f>SUM(B30:F30)</f>
         <v/>
@@ -2511,11 +2601,11 @@
           <t>VALE TRANSPORTE (compra set/26)</t>
         </is>
       </c>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
       <c r="G35" s="20">
         <f>SUM(B35:F35)</f>
         <v/>
@@ -2532,11 +2622,11 @@
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B36" s="33" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
       <c r="G36" s="20">
         <f>SUM(B36:F36)</f>
         <v/>
@@ -2713,19 +2803,19 @@
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="34" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="34" t="n">
         <v>1621</v>
       </c>
       <c r="G6" s="20">
@@ -2740,11 +2830,11 @@
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
       <c r="G7" s="20">
         <f>SUM(B7:F7)</f>
         <v/>
@@ -2757,13 +2847,13 @@
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>442.09</v>
       </c>
-      <c r="F8" s="33" t="n"/>
+      <c r="F8" s="34" t="n"/>
       <c r="G8" s="20">
         <f>SUM(B8:F8)</f>
         <v/>
@@ -2776,17 +2866,17 @@
           <t>COMISSÃO PRODUTOS + PDV</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n">
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n">
         <v>850</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="34" t="n">
         <v>908.7</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="34" t="n">
         <v>265</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="34" t="n">
         <v>122.11</v>
       </c>
       <c r="G9" s="20">
@@ -2805,17 +2895,17 @@
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n">
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n">
         <v>163.46</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="34" t="n">
         <v>174.75</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="34" t="n">
         <v>221</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="34" t="n">
         <v>23.48</v>
       </c>
       <c r="G10" s="20">
@@ -2834,11 +2924,11 @@
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="33" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
       <c r="G11" s="20">
         <f>SUM(B11:F11)</f>
         <v/>
@@ -2851,17 +2941,17 @@
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n"/>
-      <c r="C12" s="33" t="n">
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="34" t="n">
         <v>1350</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="34" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="34" t="n">
         <v>300</v>
       </c>
       <c r="G12" s="20">
@@ -2876,13 +2966,13 @@
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n">
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
       <c r="G13" s="20">
         <f>SUM(B13:F13)</f>
         <v/>
@@ -2895,11 +2985,11 @@
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="33" t="n"/>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="34" t="n"/>
       <c r="G14" s="20">
         <f>SUM(B14:F14)</f>
         <v/>
@@ -2912,11 +3002,11 @@
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
       <c r="G15" s="20">
         <f>SUM(B15:F15)</f>
         <v/>
@@ -2975,11 +3065,11 @@
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="33" t="n"/>
-      <c r="E18" s="33" t="n"/>
-      <c r="F18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
       <c r="G18" s="20">
         <f>SUM(B18:F18)</f>
         <v/>
@@ -2992,17 +3082,17 @@
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="B19" s="33" t="n"/>
-      <c r="C19" s="33" t="n">
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n">
         <v>-500</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="34" t="n">
         <v>-290</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="34" t="n">
         <v>-350</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="34" t="n">
         <v>-200</v>
       </c>
       <c r="G19" s="20">
@@ -3017,11 +3107,11 @@
           <t>DESCONTO FALTAS</t>
         </is>
       </c>
-      <c r="B20" s="33" t="n"/>
-      <c r="C20" s="33" t="n"/>
-      <c r="D20" s="33" t="n"/>
-      <c r="E20" s="33" t="n"/>
-      <c r="F20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="34" t="n"/>
       <c r="G20" s="20">
         <f>SUM(B20:F20)</f>
         <v/>
@@ -3034,11 +3124,11 @@
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="34" t="n"/>
       <c r="G21" s="20">
         <f>SUM(B21:F21)</f>
         <v/>
@@ -3051,19 +3141,19 @@
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B22" s="33" t="n">
+      <c r="B22" s="34" t="n">
         <v>-843.3099999999999</v>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C22" s="34" t="n">
         <v>-384.72</v>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="34" t="n">
         <v>-375.12</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="34" t="n">
         <v>-254.48</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="34" t="n">
         <v>-161.67</v>
       </c>
       <c r="G22" s="20">
@@ -3078,11 +3168,11 @@
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B23" s="33" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="33" t="n"/>
-      <c r="F23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
       <c r="G23" s="20">
         <f>SUM(B23:F23)</f>
         <v/>
@@ -3173,19 +3263,19 @@
           <t>SALDO FINAL DA PLANILHA ORIGINAL</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="34" t="n">
         <v>4805.1</v>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="34" t="n">
         <v>3249.74</v>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="34" t="n">
         <v>3489.33</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="34" t="n">
         <v>2444.61</v>
       </c>
-      <c r="F27" s="33" t="n">
+      <c r="F27" s="34" t="n">
         <v>1704.92</v>
       </c>
       <c r="G27" s="20">
@@ -3376,15 +3466,15 @@
           <t>VALE TRANSPORTE</t>
         </is>
       </c>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n">
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n">
         <v>750</v>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="34" t="n"/>
       <c r="G34" s="20">
         <f>SUM(B34:F34)</f>
         <v/>
@@ -3526,7 +3616,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="33">
         <f>'HOLERITE AGO.26'!B6</f>
         <v/>
       </c>
@@ -3548,7 +3638,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="33">
         <f>'HOLERITE AGO.26'!B7</f>
         <v/>
       </c>
@@ -3570,7 +3660,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="33">
         <f>'HOLERITE AGO.26'!B8</f>
         <v/>
       </c>
@@ -3592,7 +3682,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="33">
         <f>'HOLERITE AGO.26'!B11</f>
         <v/>
       </c>
@@ -3614,7 +3704,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <f>'HOLERITE AGO.26'!B12</f>
         <v/>
       </c>
@@ -3636,7 +3726,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <f>'HOLERITE AGO.26'!B13</f>
         <v/>
       </c>
@@ -3658,7 +3748,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="33">
         <f>'HOLERITE AGO.26'!B14</f>
         <v/>
       </c>
@@ -3680,7 +3770,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="33">
         <f>'HOLERITE AGO.26'!B15</f>
         <v/>
       </c>
@@ -3702,7 +3792,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <f>'HOLERITE AGO.26'!B16</f>
         <v/>
       </c>
@@ -3724,7 +3814,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="33">
         <f>'HOLERITE AGO.26'!B17</f>
         <v/>
       </c>
@@ -3746,7 +3836,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <f>'HOLERITE AGO.26'!B18</f>
         <v/>
       </c>
@@ -3768,7 +3858,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <f>'HOLERITE AGO.26'!B19</f>
         <v/>
       </c>
@@ -3790,7 +3880,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <f>'HOLERITE AGO.26'!B20</f>
         <v/>
       </c>
@@ -3812,7 +3902,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="33">
         <f>'HOLERITE AGO.26'!B21</f>
         <v/>
       </c>
@@ -3856,7 +3946,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <f>'HOLERITE AGO.26'!B24</f>
         <v/>
       </c>
@@ -3878,7 +3968,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <f>'HOLERITE AGO.26'!B25</f>
         <v/>
       </c>
@@ -3900,7 +3990,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <f>'HOLERITE AGO.26'!B26</f>
         <v/>
       </c>
@@ -3922,7 +4012,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <f>'HOLERITE AGO.26'!B27</f>
         <v/>
       </c>
@@ -3944,7 +4034,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <f>'HOLERITE AGO.26'!B28</f>
         <v/>
       </c>
@@ -3966,7 +4056,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="33">
         <f>'HOLERITE AGO.26'!B29</f>
         <v/>
       </c>
@@ -3988,7 +4078,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <f>'HOLERITE AGO.26'!B30</f>
         <v/>
       </c>
@@ -4054,7 +4144,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <f>'HOLERITE AGO.26'!C6</f>
         <v/>
       </c>
@@ -4076,7 +4166,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="33">
         <f>'HOLERITE AGO.26'!C7</f>
         <v/>
       </c>
@@ -4098,7 +4188,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="33">
         <f>'HOLERITE AGO.26'!C8</f>
         <v/>
       </c>
@@ -4120,7 +4210,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <f>'HOLERITE AGO.26'!C11</f>
         <v/>
       </c>
@@ -4142,7 +4232,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="33">
         <f>'HOLERITE AGO.26'!C12</f>
         <v/>
       </c>
@@ -4164,7 +4254,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="33">
         <f>'HOLERITE AGO.26'!C13</f>
         <v/>
       </c>
@@ -4186,7 +4276,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="33">
         <f>'HOLERITE AGO.26'!C14</f>
         <v/>
       </c>
@@ -4208,7 +4298,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="33">
         <f>'HOLERITE AGO.26'!C15</f>
         <v/>
       </c>
@@ -4230,7 +4320,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="33">
         <f>'HOLERITE AGO.26'!C16</f>
         <v/>
       </c>
@@ -4252,7 +4342,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="33">
         <f>'HOLERITE AGO.26'!C17</f>
         <v/>
       </c>
@@ -4274,7 +4364,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="33">
         <f>'HOLERITE AGO.26'!C18</f>
         <v/>
       </c>
@@ -4296,7 +4386,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="33">
         <f>'HOLERITE AGO.26'!C19</f>
         <v/>
       </c>
@@ -4318,7 +4408,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="33">
         <f>'HOLERITE AGO.26'!C20</f>
         <v/>
       </c>
@@ -4340,7 +4430,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <f>'HOLERITE AGO.26'!C21</f>
         <v/>
       </c>
@@ -4384,7 +4474,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="33">
         <f>'HOLERITE AGO.26'!C24</f>
         <v/>
       </c>
@@ -4406,7 +4496,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="33">
         <f>'HOLERITE AGO.26'!C25</f>
         <v/>
       </c>
@@ -4428,7 +4518,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="33">
         <f>'HOLERITE AGO.26'!C26</f>
         <v/>
       </c>
@@ -4450,7 +4540,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="33">
         <f>'HOLERITE AGO.26'!C27</f>
         <v/>
       </c>
@@ -4472,7 +4562,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="33">
         <f>'HOLERITE AGO.26'!C28</f>
         <v/>
       </c>
@@ -4494,7 +4584,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="33">
         <f>'HOLERITE AGO.26'!C29</f>
         <v/>
       </c>
@@ -4516,7 +4606,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="33">
         <f>'HOLERITE AGO.26'!C30</f>
         <v/>
       </c>
@@ -4582,7 +4672,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="33">
         <f>'HOLERITE AGO.26'!D6</f>
         <v/>
       </c>
@@ -4604,7 +4694,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="33">
         <f>'HOLERITE AGO.26'!D7</f>
         <v/>
       </c>
@@ -4626,7 +4716,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="33">
         <f>'HOLERITE AGO.26'!D8</f>
         <v/>
       </c>
@@ -4648,7 +4738,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="33">
         <f>'HOLERITE AGO.26'!D11</f>
         <v/>
       </c>
@@ -4670,7 +4760,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="33">
         <f>'HOLERITE AGO.26'!D12</f>
         <v/>
       </c>
@@ -4692,7 +4782,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="33">
         <f>'HOLERITE AGO.26'!D13</f>
         <v/>
       </c>
@@ -4714,7 +4804,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="33">
         <f>'HOLERITE AGO.26'!D14</f>
         <v/>
       </c>
@@ -4736,7 +4826,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="33">
         <f>'HOLERITE AGO.26'!D15</f>
         <v/>
       </c>
@@ -4758,7 +4848,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="33">
         <f>'HOLERITE AGO.26'!D16</f>
         <v/>
       </c>
@@ -4780,7 +4870,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="33">
         <f>'HOLERITE AGO.26'!D17</f>
         <v/>
       </c>
@@ -4802,7 +4892,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="33">
         <f>'HOLERITE AGO.26'!D18</f>
         <v/>
       </c>
@@ -4824,7 +4914,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="33">
         <f>'HOLERITE AGO.26'!D19</f>
         <v/>
       </c>
@@ -4846,7 +4936,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="33">
         <f>'HOLERITE AGO.26'!D20</f>
         <v/>
       </c>
@@ -4868,7 +4958,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="33">
         <f>'HOLERITE AGO.26'!D21</f>
         <v/>
       </c>
@@ -4912,7 +5002,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D70" s="34">
+      <c r="D70" s="33">
         <f>'HOLERITE AGO.26'!D24</f>
         <v/>
       </c>
@@ -4934,7 +5024,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="33">
         <f>'HOLERITE AGO.26'!D25</f>
         <v/>
       </c>
@@ -4956,7 +5046,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="33">
         <f>'HOLERITE AGO.26'!D26</f>
         <v/>
       </c>
@@ -4978,7 +5068,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D73" s="34">
+      <c r="D73" s="33">
         <f>'HOLERITE AGO.26'!D27</f>
         <v/>
       </c>
@@ -5000,7 +5090,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D74" s="34">
+      <c r="D74" s="33">
         <f>'HOLERITE AGO.26'!D28</f>
         <v/>
       </c>
@@ -5022,7 +5112,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D75" s="34">
+      <c r="D75" s="33">
         <f>'HOLERITE AGO.26'!D29</f>
         <v/>
       </c>
@@ -5044,7 +5134,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D76" s="34">
+      <c r="D76" s="33">
         <f>'HOLERITE AGO.26'!D30</f>
         <v/>
       </c>
@@ -5110,7 +5200,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D80" s="34">
+      <c r="D80" s="33">
         <f>'HOLERITE AGO.26'!E6</f>
         <v/>
       </c>
@@ -5132,7 +5222,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D81" s="34">
+      <c r="D81" s="33">
         <f>'HOLERITE AGO.26'!E7</f>
         <v/>
       </c>
@@ -5154,7 +5244,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D82" s="34">
+      <c r="D82" s="33">
         <f>'HOLERITE AGO.26'!E8</f>
         <v/>
       </c>
@@ -5176,7 +5266,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D83" s="34">
+      <c r="D83" s="33">
         <f>'HOLERITE AGO.26'!E11</f>
         <v/>
       </c>
@@ -5198,7 +5288,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D84" s="34">
+      <c r="D84" s="33">
         <f>'HOLERITE AGO.26'!E12</f>
         <v/>
       </c>
@@ -5220,7 +5310,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D85" s="34">
+      <c r="D85" s="33">
         <f>'HOLERITE AGO.26'!E13</f>
         <v/>
       </c>
@@ -5242,7 +5332,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D86" s="34">
+      <c r="D86" s="33">
         <f>'HOLERITE AGO.26'!E14</f>
         <v/>
       </c>
@@ -5264,7 +5354,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D87" s="34">
+      <c r="D87" s="33">
         <f>'HOLERITE AGO.26'!E15</f>
         <v/>
       </c>
@@ -5286,7 +5376,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D88" s="34">
+      <c r="D88" s="33">
         <f>'HOLERITE AGO.26'!E16</f>
         <v/>
       </c>
@@ -5308,7 +5398,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D89" s="34">
+      <c r="D89" s="33">
         <f>'HOLERITE AGO.26'!E17</f>
         <v/>
       </c>
@@ -5330,7 +5420,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D90" s="34">
+      <c r="D90" s="33">
         <f>'HOLERITE AGO.26'!E18</f>
         <v/>
       </c>
@@ -5352,7 +5442,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D91" s="34">
+      <c r="D91" s="33">
         <f>'HOLERITE AGO.26'!E19</f>
         <v/>
       </c>
@@ -5374,7 +5464,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D92" s="34">
+      <c r="D92" s="33">
         <f>'HOLERITE AGO.26'!E20</f>
         <v/>
       </c>
@@ -5396,7 +5486,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D93" s="34">
+      <c r="D93" s="33">
         <f>'HOLERITE AGO.26'!E21</f>
         <v/>
       </c>
@@ -5440,7 +5530,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D95" s="34">
+      <c r="D95" s="33">
         <f>'HOLERITE AGO.26'!E24</f>
         <v/>
       </c>
@@ -5462,7 +5552,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D96" s="34">
+      <c r="D96" s="33">
         <f>'HOLERITE AGO.26'!E25</f>
         <v/>
       </c>
@@ -5484,7 +5574,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D97" s="34">
+      <c r="D97" s="33">
         <f>'HOLERITE AGO.26'!E26</f>
         <v/>
       </c>
@@ -5506,7 +5596,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D98" s="34">
+      <c r="D98" s="33">
         <f>'HOLERITE AGO.26'!E27</f>
         <v/>
       </c>
@@ -5528,7 +5618,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D99" s="34">
+      <c r="D99" s="33">
         <f>'HOLERITE AGO.26'!E28</f>
         <v/>
       </c>
@@ -5550,7 +5640,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D100" s="34">
+      <c r="D100" s="33">
         <f>'HOLERITE AGO.26'!E29</f>
         <v/>
       </c>
@@ -5572,7 +5662,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D101" s="34">
+      <c r="D101" s="33">
         <f>'HOLERITE AGO.26'!E30</f>
         <v/>
       </c>
@@ -5638,7 +5728,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D105" s="34">
+      <c r="D105" s="33">
         <f>'HOLERITE AGO.26'!F6</f>
         <v/>
       </c>
@@ -5660,7 +5750,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D106" s="34">
+      <c r="D106" s="33">
         <f>'HOLERITE AGO.26'!F7</f>
         <v/>
       </c>
@@ -5682,7 +5772,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D107" s="34">
+      <c r="D107" s="33">
         <f>'HOLERITE AGO.26'!F8</f>
         <v/>
       </c>
@@ -5704,7 +5794,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D108" s="34">
+      <c r="D108" s="33">
         <f>'HOLERITE AGO.26'!F11</f>
         <v/>
       </c>
@@ -5726,7 +5816,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D109" s="34">
+      <c r="D109" s="33">
         <f>'HOLERITE AGO.26'!F12</f>
         <v/>
       </c>
@@ -5748,7 +5838,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D110" s="34">
+      <c r="D110" s="33">
         <f>'HOLERITE AGO.26'!F13</f>
         <v/>
       </c>
@@ -5770,7 +5860,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D111" s="34">
+      <c r="D111" s="33">
         <f>'HOLERITE AGO.26'!F14</f>
         <v/>
       </c>
@@ -5792,7 +5882,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D112" s="34">
+      <c r="D112" s="33">
         <f>'HOLERITE AGO.26'!F15</f>
         <v/>
       </c>
@@ -5814,7 +5904,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D113" s="34">
+      <c r="D113" s="33">
         <f>'HOLERITE AGO.26'!F16</f>
         <v/>
       </c>
@@ -5836,7 +5926,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D114" s="34">
+      <c r="D114" s="33">
         <f>'HOLERITE AGO.26'!F17</f>
         <v/>
       </c>
@@ -5858,7 +5948,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D115" s="34">
+      <c r="D115" s="33">
         <f>'HOLERITE AGO.26'!F18</f>
         <v/>
       </c>
@@ -5880,7 +5970,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D116" s="34">
+      <c r="D116" s="33">
         <f>'HOLERITE AGO.26'!F19</f>
         <v/>
       </c>
@@ -5902,7 +5992,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D117" s="34">
+      <c r="D117" s="33">
         <f>'HOLERITE AGO.26'!F20</f>
         <v/>
       </c>
@@ -5924,7 +6014,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D118" s="34">
+      <c r="D118" s="33">
         <f>'HOLERITE AGO.26'!F21</f>
         <v/>
       </c>
@@ -5968,7 +6058,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D120" s="34">
+      <c r="D120" s="33">
         <f>'HOLERITE AGO.26'!F24</f>
         <v/>
       </c>
@@ -5990,7 +6080,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D121" s="34">
+      <c r="D121" s="33">
         <f>'HOLERITE AGO.26'!F25</f>
         <v/>
       </c>
@@ -6012,7 +6102,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D122" s="34">
+      <c r="D122" s="33">
         <f>'HOLERITE AGO.26'!F26</f>
         <v/>
       </c>
@@ -6034,7 +6124,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D123" s="34">
+      <c r="D123" s="33">
         <f>'HOLERITE AGO.26'!F27</f>
         <v/>
       </c>
@@ -6056,7 +6146,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D124" s="34">
+      <c r="D124" s="33">
         <f>'HOLERITE AGO.26'!F28</f>
         <v/>
       </c>
@@ -6078,7 +6168,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D125" s="34">
+      <c r="D125" s="33">
         <f>'HOLERITE AGO.26'!F29</f>
         <v/>
       </c>
@@ -6100,7 +6190,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D126" s="34">
+      <c r="D126" s="33">
         <f>'HOLERITE AGO.26'!F30</f>
         <v/>
       </c>
@@ -6221,7 +6311,7 @@
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6232,7 +6322,7 @@
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$7:$F$7,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6243,7 +6333,7 @@
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$8:$F$8,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6254,7 +6344,7 @@
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$11:$F$11,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6265,7 +6355,7 @@
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$12:$F$12,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6276,7 +6366,7 @@
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$13:$F$13,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6287,7 +6377,7 @@
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$14:$F$14,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6298,7 +6388,7 @@
           <t>Prêmio cota geral</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$15:$F$15,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6309,7 +6399,7 @@
           <t>Prêmio pré-vencidos</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$16:$F$16,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6320,7 +6410,7 @@
           <t>Férias</t>
         </is>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6331,7 +6421,7 @@
           <t>1/3 constitucional de férias</t>
         </is>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6342,7 +6432,7 @@
           <t>Incentivo aplicações</t>
         </is>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6353,7 +6443,7 @@
           <t>Incentivo vitaminas</t>
         </is>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6364,7 +6454,7 @@
           <t>Outros incentivos</t>
         </is>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6395,7 +6485,7 @@
           <t>Adiantamento / vales</t>
         </is>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6406,7 +6496,7 @@
           <t>Adiantamento de incentivos e aplicações</t>
         </is>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$25:$F$25,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6417,7 +6507,7 @@
           <t>Convênio</t>
         </is>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$26:$F$26,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6428,7 +6518,7 @@
           <t>Faltas / atrasos</t>
         </is>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6439,7 +6529,7 @@
           <t>Vale transporte 6%</t>
         </is>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6450,7 +6540,7 @@
           <t>INSS</t>
         </is>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6461,7 +6551,7 @@
           <t>IRRF</t>
         </is>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -6510,7 +6600,7 @@
           <t>Venda bruta</t>
         </is>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$C$5:$C$9,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
@@ -6521,7 +6611,7 @@
           <t>Descontos concedidos</t>
         </is>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$D$5:$D$9,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
@@ -6532,7 +6622,7 @@
           <t>Venda líquida</t>
         </is>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$E$5:$E$9,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
@@ -6543,7 +6633,7 @@
           <t>Comissão apurada</t>
         </is>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$F$5:$F$9,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
@@ -6554,7 +6644,7 @@
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$J$5:$J$9,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
@@ -6600,4 +6690,323 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>APONTAMENTO DO PONTO — AGOSTO/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loja TRANCOSO · horas extras, adicional noturno e feriado trabalhado · alimenta a aba HOLERITE AGO.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>OCORRÊNCIA</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>QTDE</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>SALÁRIO BASE</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>VALOR UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>RUBRICA DESTINO</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>OBSERVAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Horas extras 50%</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E5" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A5,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="35">
+        <f>ROUND(E5/PARÂMETROS!$B$16*(1+PARÂMETROS!$B$17),4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>ROUND(C5*F5,2)</f>
+        <v/>
+      </c>
+      <c r="H5" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>40 horas extras normais em agosto/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="54" t="n"/>
+      <c r="B6" s="54" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="20">
+        <f>ROUND(C6*F6,2)</f>
+        <v/>
+      </c>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="54" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="n"/>
+      <c r="B7" s="54" t="n"/>
+      <c r="C7" s="54" t="n"/>
+      <c r="D7" s="54" t="n"/>
+      <c r="E7" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A7,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="20">
+        <f>ROUND(C7*F7,2)</f>
+        <v/>
+      </c>
+      <c r="H7" s="54" t="n"/>
+      <c r="I7" s="54" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="n"/>
+      <c r="B8" s="54" t="n"/>
+      <c r="C8" s="54" t="n"/>
+      <c r="D8" s="54" t="n"/>
+      <c r="E8" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A8,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="20">
+        <f>ROUND(C8*F8,2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="54" t="n"/>
+      <c r="I8" s="54" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="54" t="n"/>
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A9,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="20">
+        <f>ROUND(C9*F9,2)</f>
+        <v/>
+      </c>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="n"/>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A10,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="20">
+        <f>ROUND(C10*F10,2)</f>
+        <v/>
+      </c>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="n"/>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="54" t="n"/>
+      <c r="D11" s="54" t="n"/>
+      <c r="E11" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A11,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="20">
+        <f>ROUND(C11*F11,2)</f>
+        <v/>
+      </c>
+      <c r="H11" s="54" t="n"/>
+      <c r="I11" s="54" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="n"/>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
+      <c r="D12" s="54" t="n"/>
+      <c r="E12" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A12,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="20">
+        <f>ROUND(C12*F12,2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="n"/>
+      <c r="B13" s="54" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A13,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="20">
+        <f>ROUND(C13*F13,2)</f>
+        <v/>
+      </c>
+      <c r="H13" s="54" t="n"/>
+      <c r="I13" s="54" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="20">
+        <f>SUM(G5:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE AGO.26.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I13"/>
+  <mergeCells count="6">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -215,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -307,6 +307,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -672,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -924,7 +927,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada, para compensar o aumento da comissão dobrada.</t>
+          <t>TAMILES: atestado de 02/09 a 08/09/2026 — lançar na folha de SETEMBRO como falta justificada (abonada), sem desconto. Não entra nesta folha de agosto.</t>
         </is>
       </c>
     </row>
@@ -936,37 +939,41 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada, para compensar o aumento da comissão dobrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
           <t>UILLIAN também registra vendas no relatório da loja Centro — conferir se alguma comissão deve ser rateada entre as lojas.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -974,7 +981,7 @@
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -982,7 +989,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -990,7 +997,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -998,7 +1005,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1006,13 +1013,21 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>PONTO AGO.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
@@ -1024,11 +1039,11 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6698,7 +6713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6997,14 +7012,50 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>OCORRÊNCIAS PARA A PRÓXIMA COMPETÊNCIA (SETEMBRO/2026) — NÃO ENTRAM NESTA FOLHA</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>Atestado médico de 7 dias, entregue em 02/09/2026 — cobre de 02/09 a 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Cai na competência SETEMBRO/2026 (holerite pago em 05/10/2026), não nesta folha de agosto. Atestado de até 15 dias é abonado pela empresa: falta justificada, sem desconto de salário nem de DSR. A partir do 16º dia seria auxílio-doença pelo INSS. Anexar o atestado à pasta da funcionária.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:I13"/>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -1999,9 +1999,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
-        <f> COMISSÃO TOTAL</f>
-        <v/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>COMISSÃO TOTAL (soma)</t>
+        </is>
       </c>
       <c r="B11" s="20">
         <f>SUM(B9:B10)</f>
@@ -2063,9 +2064,10 @@
         <f>SUM(B12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="32">
-        <f> (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026.</f>
-        <v/>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>Cálculo: (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2468,7 +2470,7 @@
       </c>
       <c r="H28" s="32" t="inlineStr">
         <is>
-          <t>Valores praticados em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
+          <t>Valores praticados em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. Quem passou o mês em férias fica sem desconto.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$H$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
@@ -1756,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2357,7 +2357,7 @@
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="B24" s="34" t="n"/>
@@ -2654,71 +2654,92 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B38" s="38" t="inlineStr"/>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="31">
+        <f>SUM(B37:F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. Não houve férias nesta loja em agosto/2026. RENALDO (Centro) e VALDICK (Trancoso) entram de férias em 01/09 — ver a folha de setembro.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B39" s="38" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B42" s="38" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H36"/>
+  <autoFilter ref="A4:H37"/>
   <mergeCells count="7">
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B38:H38"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3955,7 +3976,7 @@
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
@@ -4483,7 +4504,7 @@
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C45" s="29" t="inlineStr">
@@ -5011,7 +5032,7 @@
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
@@ -5539,7 +5560,7 @@
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C95" s="29" t="inlineStr">
@@ -6067,7 +6088,7 @@
       </c>
       <c r="B120" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C120" s="29" t="inlineStr">
@@ -6499,7 +6520,7 @@
     <row r="23">
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>Adiantamento / vales</t>
+          <t>Adiantamento salarial / vales</t>
         </is>
       </c>
       <c r="C23" s="33">

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$H$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
@@ -180,12 +180,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FFF0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F0"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -215,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -228,7 +228,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -282,8 +282,10 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -294,20 +296,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -675,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -836,7 +838,7 @@
       <c r="A22" s="4" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>TRANCOSO PAGA O DOBRO DA COMISSÃO APURADA: a linha COMISSÃO PRODUTOS já multiplica por 2 o valor do InovaFarma (multiplicador na aba PARÂMETROS).</t>
+          <t>Os prêmios, vales, INSS e IRRF vieram do holerite de agosto emitido pela Betel Contabilidade. A linha DIFERENÇA fecha em zero para os cinco.</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Os incentivos são simples: entram pelo valor apurado, sem dobrar.</t>
+          <t>TRANCOSO PAGA O DOBRO DA COMISSÃO APURADA: a linha COMISSÃO PRODUTOS já multiplica por 2 o valor do InovaFarma (multiplicador na aba PARÂMETROS).</t>
         </is>
       </c>
     </row>
@@ -852,7 +854,7 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Em julho/2026 a comissão foi lançada por média. Com a comissão dobrada a partir de agosto, a empresa vai reduzir nas premiações a diferença.</t>
+          <t>Os incentivos são simples: entram pelo valor apurado, sem dobrar.</t>
         </is>
       </c>
     </row>
@@ -860,26 +862,22 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>Em julho/2026 a comissão foi lançada por média. Com a comissão dobrada a partir de agosto, a empresa vai reduzir nas premiações a diferença.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>UILLIAN: não recebe comissão sobre vendas (mesmo critério de julho/2026) — a rubrica fica zerada e o apurado dele aparece só na aba BASE.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras, adicional noturno e feriados trabalhados de agosto — lançar na aba PONTO AGO.26.</t>
         </is>
       </c>
     </row>
@@ -891,7 +889,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Horas extras, adicional noturno e feriados trabalhados de agosto — lançar na aba PONTO AGO.26.</t>
         </is>
       </c>
     </row>
@@ -903,7 +901,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -915,7 +913,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -927,7 +925,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TAMILES: atestado de 02/09 a 08/09/2026 — lançar na folha de SETEMBRO como falta justificada (abonada), sem desconto. Não entra nesta folha de agosto.</t>
+          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
         </is>
       </c>
     </row>
@@ -939,7 +937,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada, para compensar o aumento da comissão dobrada.</t>
+          <t>TAMILES: atestado de 02/09 a 08/09/2026 — lançar na folha de SETEMBRO como falta justificada (abonada), sem desconto. Não entra nesta folha de agosto.</t>
         </is>
       </c>
     </row>
@@ -951,37 +949,41 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada, para compensar o aumento da comissão dobrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>UILLIAN também registra vendas no relatório da loja Centro — conferir se alguma comissão deve ser rateada entre as lojas.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -989,7 +991,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -997,7 +999,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1007,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1015,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1023,7 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>JULHO.26 REVISADO — a folha de julho (TRANCOSO JULHO) reorganizada e conferida.</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1031,14 @@
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>PONTO AGO.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
       </c>
@@ -1036,14 +1046,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1756,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2073,49 +2083,51 @@
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>AUXÍLIO GERÊNCIA</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="34" t="n"/>
-      <c r="G13" s="20">
+          <t>DSR SOBRE HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="37">
         <f>SUM(B13:F13)</f>
         <v/>
       </c>
       <c r="H13" s="32" t="inlineStr">
         <is>
-          <t>Conforme acordo da loja.</t>
+          <t>Rubrica 057 do holerite da Betel. ATENÇÃO: a rubrica 420 acima já leva as horas extras na base, então este valor paga o DSR das horas extras uma segunda vez — conferir com a contabilidade.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ADICIONAL PRÊMIO META CAIXA</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="34" t="n"/>
-      <c r="G14" s="20">
+          <t>SALÁRIO FAMÍLIA</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="31">
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
       <c r="H14" s="32" t="inlineStr">
         <is>
-          <t>Conforme apuração do caixa.</t>
+          <t>Rubrica 599 do holerite da Betel.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>PRÊMIO COTA GERAL</t>
+          <t>INSUFICIÊNCIA DE SALDO</t>
         </is>
       </c>
       <c r="B15" s="30" t="n"/>
@@ -2129,14 +2141,14 @@
       </c>
       <c r="H15" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER conforme a tabela de metas da loja (aba METAS da planilha original). Lançar já com a redução combinada para compensar o aumento da comissão dobrada.</t>
+          <t>Rubrica 998 do holerite da Betel — contrapartida do vale-transporte de quem ficou sem saldo.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
+          <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
       <c r="B16" s="34" t="n"/>
@@ -2150,14 +2162,14 @@
       </c>
       <c r="H16" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER conforme a apuração de pré-vencidos de agosto.</t>
+          <t>Conforme acordo da loja.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>FÉRIAS (DIAS GOZADOS)</t>
+          <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
       <c r="B17" s="34" t="n"/>
@@ -2171,163 +2183,126 @@
       </c>
       <c r="H17" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER se houve férias no mês; informar o período.</t>
+          <t>Conforme apuração do caixa.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="n"/>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n"/>
-      <c r="F18" s="34" t="n"/>
-      <c r="G18" s="20">
+          <t>PRÊMIO COTA GERAL / BONIFICAÇÃO</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="31">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="32" t="inlineStr">
         <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+          <t>Rubrica 011 (Bonificação/Prêmios) do holerite da Betel — já engloba cota geral e pré-vencidos. Lançar já com a redução combinada pela comissão dobrada.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="B19" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!G5</f>
-        <v/>
-      </c>
-      <c r="C19" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!G6</f>
-        <v/>
-      </c>
-      <c r="D19" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E19" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!G8</f>
-        <v/>
-      </c>
-      <c r="F19" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!G9</f>
-        <v/>
-      </c>
+          <t>PRÊMIO PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="34" t="n"/>
       <c r="G19" s="20">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
       <c r="H19" s="32" t="inlineStr">
         <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
+          <t>Vem somado na linha acima, na rubrica 011 do holerite.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B20" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C20" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D20" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F20" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!H9</f>
-        <v/>
-      </c>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="34" t="n"/>
       <c r="G20" s="20">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
       <c r="H20" s="32" t="inlineStr">
         <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+          <t>PREENCHER se houve férias no mês; informar o período.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B21" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C21" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D21" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E21" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F21" s="33">
-        <f>'BASE INOVAFARMA AGO.26'!I9</f>
-        <v/>
-      </c>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="34" t="n"/>
       <c r="G21" s="20">
         <f>SUM(B21:F21)</f>
         <v/>
       </c>
       <c r="H21" s="32" t="inlineStr">
         <is>
-          <t>Populares, oficinais e similar normal.</t>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>SUM(B6:B21)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>SUM(C6:C21)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f>SUM(D6:D21)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="20">
-        <f>SUM(E6:E21)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F22" s="20">
-        <f>SUM(F6:F21)-F9-F10</f>
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!G5</f>
+        <v/>
+      </c>
+      <c r="C22" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!G6</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!G8</f>
+        <v/>
+      </c>
+      <c r="F22" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!G9</f>
         <v/>
       </c>
       <c r="G22" s="20">
@@ -2336,148 +2311,199 @@
       </c>
       <c r="H22" s="32" t="inlineStr">
         <is>
-          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>DESCONTOS  (lançar com sinal negativo)</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="n"/>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="28" t="n"/>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="n"/>
+          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B23" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C23" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D23" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E23" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F23" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!H9</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>SUM(B23:F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="32" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="n"/>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B24" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C24" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D24" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E24" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F24" s="33">
+        <f>'BASE INOVAFARMA AGO.26'!I9</f>
+        <v/>
+      </c>
       <c r="G24" s="20">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER com os vales adiantados durante agosto.</t>
+          <t>Populares, oficinais e similar normal.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B25" s="36">
-        <f>-(B19+B20+B21)</f>
-        <v/>
-      </c>
-      <c r="C25" s="36">
-        <f>-(C19+C20+C21)</f>
-        <v/>
-      </c>
-      <c r="D25" s="36">
-        <f>-(D19+D20+D21)</f>
-        <v/>
-      </c>
-      <c r="E25" s="36">
-        <f>-(E19+E20+E21)</f>
-        <v/>
-      </c>
-      <c r="F25" s="36">
-        <f>-(F19+F20+F21)</f>
-        <v/>
-      </c>
-      <c r="G25" s="31">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B25" s="20">
+        <f>SUM(B6:B24)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>SUM(C6:C24)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f>SUM(D6:D24)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E25" s="20">
+        <f>SUM(E6:E24)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F25" s="20">
+        <f>SUM(F6:F24)-F9-F10</f>
+        <v/>
+      </c>
+      <c r="G25" s="20">
         <f>SUM(B25:F25)</f>
         <v/>
       </c>
       <c r="H25" s="32" t="inlineStr">
         <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="n"/>
-      <c r="C26" s="34" t="n"/>
-      <c r="D26" s="34" t="n"/>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="34" t="n"/>
-      <c r="G26" s="20">
-        <f>SUM(B26:F26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o convênio de agosto.</t>
-        </is>
-      </c>
+          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>DESCONTOS  (lançar com sinal negativo)</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>DESCONTO FALTAS / ATRASOS</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="20">
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="n">
+        <v>-810</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>-465</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>-580</v>
+      </c>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="31">
         <f>SUM(B27:F27)</f>
         <v/>
       </c>
       <c r="H27" s="32" t="inlineStr">
         <is>
-          <t>PREENCHER conforme o ponto.</t>
+          <t>Rubrica 630 (Desconto - verbas / Adiantamento) do holerite da Betel.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B28" s="38">
+        <f>-(B22+B23+B24)</f>
+        <v/>
+      </c>
+      <c r="C28" s="38">
+        <f>-(C22+C23+C24)</f>
+        <v/>
+      </c>
+      <c r="D28" s="38">
+        <f>-(D22+D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E28" s="38">
+        <f>-(E22+E23+E24)</f>
+        <v/>
+      </c>
+      <c r="F28" s="38">
+        <f>-(F22+F23+F24)</f>
+        <v/>
+      </c>
       <c r="G28" s="31">
         <f>SUM(B28:F28)</f>
         <v/>
       </c>
       <c r="H28" s="32" t="inlineStr">
         <is>
-          <t>Valores praticados em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. Quem passou o mês em férias fica sem desconto.</t>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>DESCONTO INSS</t>
+          <t>CONVÊNIO</t>
         </is>
       </c>
       <c r="B29" s="34" t="n"/>
@@ -2491,14 +2517,14 @@
       </c>
       <c r="H29" s="32" t="inlineStr">
         <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+          <t>PREENCHER conforme o convênio de agosto.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>DESCONTO IRRF</t>
+          <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
       <c r="B30" s="34" t="n"/>
@@ -2512,235 +2538,377 @@
       </c>
       <c r="H30" s="32" t="inlineStr">
         <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="31">
+        <f>SUM(B31:F31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="32" t="inlineStr">
+        <is>
+          <t>Rubrica 604 do holerite da Betel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>-592.27</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>-343.29</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>-348.72</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>-236.18</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>-157.52</v>
+      </c>
+      <c r="G32" s="31">
+        <f>SUM(B32:F32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>Rubrica 903 do holerite da Betel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="31">
+        <f>SUM(B33:F33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>Rubrica 914 do holerite da Betel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="B31" s="20">
-        <f>SUM(B24:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="20">
-        <f>SUM(C24:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="20">
-        <f>SUM(D24:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="20">
-        <f>SUM(E24:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f>SUM(F24:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="20">
-        <f>SUM(B31:F31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="32" t="inlineStr"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B34" s="20">
+        <f>SUM(B27:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f>SUM(C27:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="20">
+        <f>SUM(E27:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="20">
+        <f>SUM(F27:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="20">
+        <f>SUM(B34:F34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="32" t="inlineStr"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n"/>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
+      <c r="H35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER (05/09/2026)</t>
         </is>
       </c>
-      <c r="B33" s="37">
-        <f>B22+B31</f>
-        <v/>
-      </c>
-      <c r="C33" s="37">
-        <f>C22+C31</f>
-        <v/>
-      </c>
-      <c r="D33" s="37">
-        <f>D22+D31</f>
-        <v/>
-      </c>
-      <c r="E33" s="37">
-        <f>E22+E31</f>
-        <v/>
-      </c>
-      <c r="F33" s="37">
-        <f>F22+F31</f>
-        <v/>
-      </c>
-      <c r="G33" s="37">
-        <f>SUM(B33:F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="B36" s="39">
+        <f>B25+B34</f>
+        <v/>
+      </c>
+      <c r="C36" s="39">
+        <f>C25+C34</f>
+        <v/>
+      </c>
+      <c r="D36" s="39">
+        <f>D25+D34</f>
+        <v/>
+      </c>
+      <c r="E36" s="39">
+        <f>E25+E34</f>
+        <v/>
+      </c>
+      <c r="F36" s="39">
+        <f>F25+F34</f>
+        <v/>
+      </c>
+      <c r="G36" s="39">
+        <f>SUM(B36:F36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="n"/>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>VALE TRANSPORTE (compra set/26)</t>
-        </is>
-      </c>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="20">
-        <f>SUM(B35:F35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER com as passagens compradas para setembro/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
-        </is>
-      </c>
-      <c r="B36" s="34" t="n"/>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="20">
-        <f>SUM(B36:F36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme escala de domingos e feriados.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
+          <t>LÍQUIDO DO HOLERITE (BETEL)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>3995.1</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>2980.92</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>2905.76</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>2658.33</v>
+      </c>
+      <c r="F37" s="30" t="n">
+        <v>1862.94</v>
+      </c>
       <c r="G37" s="31">
         <f>SUM(B37:F37)</f>
         <v/>
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
+          <t>Valor líquido do demonstrativo emitido pela Betel Contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>DIFERENÇA (planilha − holerite)</t>
+        </is>
+      </c>
+      <c r="B38" s="20">
+        <f>ROUND(B36-B37,2)</f>
+        <v/>
+      </c>
+      <c r="C38" s="20">
+        <f>ROUND(C36-C37,2)</f>
+        <v/>
+      </c>
+      <c r="D38" s="20">
+        <f>ROUND(D36-D37,2)</f>
+        <v/>
+      </c>
+      <c r="E38" s="20">
+        <f>ROUND(E36-E37,2)</f>
+        <v/>
+      </c>
+      <c r="F38" s="20">
+        <f>ROUND(F36-F37,2)</f>
+        <v/>
+      </c>
+      <c r="G38" s="20">
+        <f>SUM(B38:F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>Deve ser zero. Os incentivos entram como provento e como desconto, então não afetam o líquido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>VALE TRANSPORTE (compra set/26)</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="n"/>
+      <c r="C40" s="34" t="n"/>
+      <c r="D40" s="34" t="n"/>
+      <c r="E40" s="34" t="n"/>
+      <c r="F40" s="34" t="n"/>
+      <c r="G40" s="20">
+        <f>SUM(B40:F40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>PREENCHER com as passagens compradas para setembro/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="34" t="n"/>
+      <c r="E41" s="34" t="n"/>
+      <c r="F41" s="34" t="n"/>
+      <c r="G41" s="20">
+        <f>SUM(B41:F41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme escala de domingos e feriados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="30" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="31">
+        <f>SUM(B42:F42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="32" t="inlineStr">
+        <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. Não houve férias nesta loja em agosto/2026. RENALDO (Centro) e VALDICK (Trancoso) entram de férias em 01/09 — ver a folha de setembro.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>LEGENDA</t>
         </is>
       </c>
-      <c r="B39" s="38" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Célula amarela, texto azul</t>
         </is>
       </c>
-      <c r="B40" s="38" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Célula laranja</t>
         </is>
       </c>
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Texto verde</t>
         </is>
       </c>
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H37"/>
+  <autoFilter ref="A4:H42"/>
   <mergeCells count="7">
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3269,27 +3437,27 @@
           <t>LÍQUIDO PAGO (05/08/2026)</t>
         </is>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="39">
         <f>B16+B24</f>
         <v/>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="39">
         <f>C16+C24</f>
         <v/>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="39">
         <f>D16+D24</f>
         <v/>
       </c>
-      <c r="E26" s="37">
+      <c r="E26" s="39">
         <f>E16+E24</f>
         <v/>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="39">
         <f>F16+F24</f>
         <v/>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="39">
         <f>SUM(B26:F26)</f>
         <v/>
       </c>
@@ -3524,42 +3692,42 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO: em julho/2026 a comissão foi lançada por uma MÉDIA, e não pelo apurado do sistema. A partir de agosto/2026 a loja passa a pagar a comissão em dobro, e a empresa vai reduzir nas premiações a diferença gerada por esse aumento.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>AJUSTES FEITOS NESTA REVISÃO (a planilha original continua intacta):</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>1. Rubricas separadas em PROVENTOS × DESCONTOS, com subtotais próprios.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>2. Nomes de rubrica padronizados e coluna de observação com a origem de cada valor.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>3. Conferência do DSR: em julho foi usado o fator de agosto (5/26) em vez de 4/27.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>4. Linha de conferência comparando o líquido revisado com o SALDO FINAL da planilha original (tem que fechar em zero).</t>
         </is>
@@ -3658,7 +3826,7 @@
         <f>'HOLERITE AGO.26'!B6</f>
         <v/>
       </c>
-      <c r="E5" s="41" t="n"/>
+      <c r="E5" s="43" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -3680,7 +3848,7 @@
         <f>'HOLERITE AGO.26'!B7</f>
         <v/>
       </c>
-      <c r="E6" s="41" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -3702,7 +3870,7 @@
         <f>'HOLERITE AGO.26'!B8</f>
         <v/>
       </c>
-      <c r="E7" s="41" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3724,7 +3892,7 @@
         <f>'HOLERITE AGO.26'!B11</f>
         <v/>
       </c>
-      <c r="E8" s="41" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3746,7 +3914,7 @@
         <f>'HOLERITE AGO.26'!B12</f>
         <v/>
       </c>
-      <c r="E9" s="41" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3765,10 +3933,10 @@
         </is>
       </c>
       <c r="D10" s="33">
-        <f>'HOLERITE AGO.26'!B13</f>
-        <v/>
-      </c>
-      <c r="E10" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B16</f>
+        <v/>
+      </c>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3787,10 +3955,10 @@
         </is>
       </c>
       <c r="D11" s="33">
-        <f>'HOLERITE AGO.26'!B14</f>
-        <v/>
-      </c>
-      <c r="E11" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B17</f>
+        <v/>
+      </c>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3809,10 +3977,10 @@
         </is>
       </c>
       <c r="D12" s="33">
-        <f>'HOLERITE AGO.26'!B15</f>
-        <v/>
-      </c>
-      <c r="E12" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B18</f>
+        <v/>
+      </c>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
@@ -3831,10 +3999,10 @@
         </is>
       </c>
       <c r="D13" s="33">
-        <f>'HOLERITE AGO.26'!B16</f>
-        <v/>
-      </c>
-      <c r="E13" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
@@ -3853,10 +4021,10 @@
         </is>
       </c>
       <c r="D14" s="33">
-        <f>'HOLERITE AGO.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
@@ -3875,10 +4043,10 @@
         </is>
       </c>
       <c r="D15" s="33">
-        <f>'HOLERITE AGO.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
@@ -3897,10 +4065,10 @@
         </is>
       </c>
       <c r="D16" s="33">
-        <f>'HOLERITE AGO.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B22</f>
+        <v/>
+      </c>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
@@ -3919,10 +4087,10 @@
         </is>
       </c>
       <c r="D17" s="33">
-        <f>'HOLERITE AGO.26'!B20</f>
-        <v/>
-      </c>
-      <c r="E17" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B23</f>
+        <v/>
+      </c>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -3941,29 +4109,29 @@
         </is>
       </c>
       <c r="D18" s="33">
-        <f>'HOLERITE AGO.26'!B21</f>
-        <v/>
-      </c>
-      <c r="E18" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B24</f>
+        <v/>
+      </c>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D19" s="43">
-        <f>'HOLERITE AGO.26'!B22</f>
+      <c r="D19" s="45">
+        <f>'HOLERITE AGO.26'!B25</f>
         <v/>
       </c>
       <c r="E19" s="18" t="n"/>
@@ -3985,10 +4153,10 @@
         </is>
       </c>
       <c r="D20" s="33">
-        <f>'HOLERITE AGO.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E20" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
@@ -4007,10 +4175,10 @@
         </is>
       </c>
       <c r="D21" s="33">
-        <f>'HOLERITE AGO.26'!B25</f>
-        <v/>
-      </c>
-      <c r="E21" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
@@ -4029,10 +4197,10 @@
         </is>
       </c>
       <c r="D22" s="33">
-        <f>'HOLERITE AGO.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
@@ -4051,10 +4219,10 @@
         </is>
       </c>
       <c r="D23" s="33">
-        <f>'HOLERITE AGO.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
@@ -4073,10 +4241,10 @@
         </is>
       </c>
       <c r="D24" s="33">
-        <f>'HOLERITE AGO.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B31</f>
+        <v/>
+      </c>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
@@ -4095,10 +4263,10 @@
         </is>
       </c>
       <c r="D25" s="33">
-        <f>'HOLERITE AGO.26'!B29</f>
-        <v/>
-      </c>
-      <c r="E25" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B32</f>
+        <v/>
+      </c>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
@@ -4117,54 +4285,54 @@
         </is>
       </c>
       <c r="D26" s="33">
-        <f>'HOLERITE AGO.26'!B30</f>
-        <v/>
-      </c>
-      <c r="E26" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!B33</f>
+        <v/>
+      </c>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="inlineStr">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C27" s="42" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D27" s="43">
-        <f>'HOLERITE AGO.26'!B31</f>
+      <c r="D27" s="45">
+        <f>'HOLERITE AGO.26'!B34</f>
         <v/>
       </c>
       <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="A28" s="46" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D28" s="46">
-        <f>'HOLERITE AGO.26'!B33</f>
-        <v/>
-      </c>
-      <c r="E28" s="47" t="n"/>
+      <c r="D28" s="48">
+        <f>'HOLERITE AGO.26'!B36</f>
+        <v/>
+      </c>
+      <c r="E28" s="49" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
@@ -4186,7 +4354,7 @@
         <f>'HOLERITE AGO.26'!C6</f>
         <v/>
       </c>
-      <c r="E30" s="41" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
@@ -4208,7 +4376,7 @@
         <f>'HOLERITE AGO.26'!C7</f>
         <v/>
       </c>
-      <c r="E31" s="41" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
@@ -4230,7 +4398,7 @@
         <f>'HOLERITE AGO.26'!C8</f>
         <v/>
       </c>
-      <c r="E32" s="41" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
@@ -4252,7 +4420,7 @@
         <f>'HOLERITE AGO.26'!C11</f>
         <v/>
       </c>
-      <c r="E33" s="41" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
@@ -4274,7 +4442,7 @@
         <f>'HOLERITE AGO.26'!C12</f>
         <v/>
       </c>
-      <c r="E34" s="41" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
@@ -4293,10 +4461,10 @@
         </is>
       </c>
       <c r="D35" s="33">
-        <f>'HOLERITE AGO.26'!C13</f>
-        <v/>
-      </c>
-      <c r="E35" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C16</f>
+        <v/>
+      </c>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
@@ -4315,10 +4483,10 @@
         </is>
       </c>
       <c r="D36" s="33">
-        <f>'HOLERITE AGO.26'!C14</f>
-        <v/>
-      </c>
-      <c r="E36" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C17</f>
+        <v/>
+      </c>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
@@ -4337,10 +4505,10 @@
         </is>
       </c>
       <c r="D37" s="33">
-        <f>'HOLERITE AGO.26'!C15</f>
-        <v/>
-      </c>
-      <c r="E37" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C18</f>
+        <v/>
+      </c>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
@@ -4359,10 +4527,10 @@
         </is>
       </c>
       <c r="D38" s="33">
-        <f>'HOLERITE AGO.26'!C16</f>
-        <v/>
-      </c>
-      <c r="E38" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
@@ -4381,10 +4549,10 @@
         </is>
       </c>
       <c r="D39" s="33">
-        <f>'HOLERITE AGO.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E39" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E39" s="43" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
@@ -4403,10 +4571,10 @@
         </is>
       </c>
       <c r="D40" s="33">
-        <f>'HOLERITE AGO.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E40" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E40" s="43" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
@@ -4425,10 +4593,10 @@
         </is>
       </c>
       <c r="D41" s="33">
-        <f>'HOLERITE AGO.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E41" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C22</f>
+        <v/>
+      </c>
+      <c r="E41" s="43" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
@@ -4447,10 +4615,10 @@
         </is>
       </c>
       <c r="D42" s="33">
-        <f>'HOLERITE AGO.26'!C20</f>
-        <v/>
-      </c>
-      <c r="E42" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C23</f>
+        <v/>
+      </c>
+      <c r="E42" s="43" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
@@ -4469,29 +4637,29 @@
         </is>
       </c>
       <c r="D43" s="33">
-        <f>'HOLERITE AGO.26'!C21</f>
-        <v/>
-      </c>
-      <c r="E43" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C24</f>
+        <v/>
+      </c>
+      <c r="E43" s="43" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="42" t="inlineStr">
+      <c r="A44" s="44" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B44" s="42" t="inlineStr">
+      <c r="B44" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C44" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D44" s="43">
-        <f>'HOLERITE AGO.26'!C22</f>
+      <c r="D44" s="45">
+        <f>'HOLERITE AGO.26'!C25</f>
         <v/>
       </c>
       <c r="E44" s="18" t="n"/>
@@ -4513,10 +4681,10 @@
         </is>
       </c>
       <c r="D45" s="33">
-        <f>'HOLERITE AGO.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E45" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E45" s="43" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
@@ -4535,10 +4703,10 @@
         </is>
       </c>
       <c r="D46" s="33">
-        <f>'HOLERITE AGO.26'!C25</f>
-        <v/>
-      </c>
-      <c r="E46" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E46" s="43" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
@@ -4557,10 +4725,10 @@
         </is>
       </c>
       <c r="D47" s="33">
-        <f>'HOLERITE AGO.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E47" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E47" s="43" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
@@ -4579,10 +4747,10 @@
         </is>
       </c>
       <c r="D48" s="33">
-        <f>'HOLERITE AGO.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E48" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E48" s="43" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
@@ -4601,10 +4769,10 @@
         </is>
       </c>
       <c r="D49" s="33">
-        <f>'HOLERITE AGO.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E49" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C31</f>
+        <v/>
+      </c>
+      <c r="E49" s="43" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
@@ -4623,10 +4791,10 @@
         </is>
       </c>
       <c r="D50" s="33">
-        <f>'HOLERITE AGO.26'!C29</f>
-        <v/>
-      </c>
-      <c r="E50" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C32</f>
+        <v/>
+      </c>
+      <c r="E50" s="43" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
@@ -4645,54 +4813,54 @@
         </is>
       </c>
       <c r="D51" s="33">
-        <f>'HOLERITE AGO.26'!C30</f>
-        <v/>
-      </c>
-      <c r="E51" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!C33</f>
+        <v/>
+      </c>
+      <c r="E51" s="43" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="42" t="inlineStr">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C52" s="42" t="inlineStr">
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D52" s="43">
-        <f>'HOLERITE AGO.26'!C31</f>
+      <c r="D52" s="45">
+        <f>'HOLERITE AGO.26'!C34</f>
         <v/>
       </c>
       <c r="E52" s="18" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="46" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B53" s="45" t="inlineStr">
+      <c r="B53" s="47" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C53" s="45" t="inlineStr">
+      <c r="C53" s="47" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D53" s="46">
-        <f>'HOLERITE AGO.26'!C33</f>
-        <v/>
-      </c>
-      <c r="E53" s="47" t="n"/>
+      <c r="D53" s="48">
+        <f>'HOLERITE AGO.26'!C36</f>
+        <v/>
+      </c>
+      <c r="E53" s="49" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
@@ -4714,7 +4882,7 @@
         <f>'HOLERITE AGO.26'!D6</f>
         <v/>
       </c>
-      <c r="E55" s="41" t="n"/>
+      <c r="E55" s="43" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
@@ -4736,7 +4904,7 @@
         <f>'HOLERITE AGO.26'!D7</f>
         <v/>
       </c>
-      <c r="E56" s="41" t="n"/>
+      <c r="E56" s="43" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
@@ -4758,7 +4926,7 @@
         <f>'HOLERITE AGO.26'!D8</f>
         <v/>
       </c>
-      <c r="E57" s="41" t="n"/>
+      <c r="E57" s="43" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
@@ -4780,7 +4948,7 @@
         <f>'HOLERITE AGO.26'!D11</f>
         <v/>
       </c>
-      <c r="E58" s="41" t="n"/>
+      <c r="E58" s="43" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
@@ -4802,7 +4970,7 @@
         <f>'HOLERITE AGO.26'!D12</f>
         <v/>
       </c>
-      <c r="E59" s="41" t="n"/>
+      <c r="E59" s="43" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
@@ -4821,10 +4989,10 @@
         </is>
       </c>
       <c r="D60" s="33">
-        <f>'HOLERITE AGO.26'!D13</f>
-        <v/>
-      </c>
-      <c r="E60" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D16</f>
+        <v/>
+      </c>
+      <c r="E60" s="43" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
@@ -4843,10 +5011,10 @@
         </is>
       </c>
       <c r="D61" s="33">
-        <f>'HOLERITE AGO.26'!D14</f>
-        <v/>
-      </c>
-      <c r="E61" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D17</f>
+        <v/>
+      </c>
+      <c r="E61" s="43" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
@@ -4865,10 +5033,10 @@
         </is>
       </c>
       <c r="D62" s="33">
-        <f>'HOLERITE AGO.26'!D15</f>
-        <v/>
-      </c>
-      <c r="E62" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D18</f>
+        <v/>
+      </c>
+      <c r="E62" s="43" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
@@ -4887,10 +5055,10 @@
         </is>
       </c>
       <c r="D63" s="33">
-        <f>'HOLERITE AGO.26'!D16</f>
-        <v/>
-      </c>
-      <c r="E63" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E63" s="43" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
@@ -4909,10 +5077,10 @@
         </is>
       </c>
       <c r="D64" s="33">
-        <f>'HOLERITE AGO.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E64" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E64" s="43" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
@@ -4931,10 +5099,10 @@
         </is>
       </c>
       <c r="D65" s="33">
-        <f>'HOLERITE AGO.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E65" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E65" s="43" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
@@ -4953,10 +5121,10 @@
         </is>
       </c>
       <c r="D66" s="33">
-        <f>'HOLERITE AGO.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E66" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D22</f>
+        <v/>
+      </c>
+      <c r="E66" s="43" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
@@ -4975,10 +5143,10 @@
         </is>
       </c>
       <c r="D67" s="33">
-        <f>'HOLERITE AGO.26'!D20</f>
-        <v/>
-      </c>
-      <c r="E67" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D23</f>
+        <v/>
+      </c>
+      <c r="E67" s="43" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
@@ -4997,29 +5165,29 @@
         </is>
       </c>
       <c r="D68" s="33">
-        <f>'HOLERITE AGO.26'!D21</f>
-        <v/>
-      </c>
-      <c r="E68" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D24</f>
+        <v/>
+      </c>
+      <c r="E68" s="43" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="42" t="inlineStr">
+      <c r="A69" s="44" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B69" s="42" t="inlineStr">
+      <c r="B69" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C69" s="42" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D69" s="43">
-        <f>'HOLERITE AGO.26'!D22</f>
+      <c r="D69" s="45">
+        <f>'HOLERITE AGO.26'!D25</f>
         <v/>
       </c>
       <c r="E69" s="18" t="n"/>
@@ -5041,10 +5209,10 @@
         </is>
       </c>
       <c r="D70" s="33">
-        <f>'HOLERITE AGO.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E70" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E70" s="43" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
@@ -5063,10 +5231,10 @@
         </is>
       </c>
       <c r="D71" s="33">
-        <f>'HOLERITE AGO.26'!D25</f>
-        <v/>
-      </c>
-      <c r="E71" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E71" s="43" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
@@ -5085,10 +5253,10 @@
         </is>
       </c>
       <c r="D72" s="33">
-        <f>'HOLERITE AGO.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E72" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E72" s="43" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
@@ -5107,10 +5275,10 @@
         </is>
       </c>
       <c r="D73" s="33">
-        <f>'HOLERITE AGO.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E73" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E73" s="43" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
@@ -5129,10 +5297,10 @@
         </is>
       </c>
       <c r="D74" s="33">
-        <f>'HOLERITE AGO.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E74" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D31</f>
+        <v/>
+      </c>
+      <c r="E74" s="43" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
@@ -5151,10 +5319,10 @@
         </is>
       </c>
       <c r="D75" s="33">
-        <f>'HOLERITE AGO.26'!D29</f>
-        <v/>
-      </c>
-      <c r="E75" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D32</f>
+        <v/>
+      </c>
+      <c r="E75" s="43" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
@@ -5173,54 +5341,54 @@
         </is>
       </c>
       <c r="D76" s="33">
-        <f>'HOLERITE AGO.26'!D30</f>
-        <v/>
-      </c>
-      <c r="E76" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!D33</f>
+        <v/>
+      </c>
+      <c r="E76" s="43" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="42" t="inlineStr">
+      <c r="A77" s="44" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B77" s="42" t="inlineStr">
+      <c r="B77" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C77" s="42" t="inlineStr">
+      <c r="C77" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D77" s="43">
-        <f>'HOLERITE AGO.26'!D31</f>
+      <c r="D77" s="45">
+        <f>'HOLERITE AGO.26'!D34</f>
         <v/>
       </c>
       <c r="E77" s="18" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="44" t="inlineStr">
+      <c r="A78" s="46" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B78" s="45" t="inlineStr">
+      <c r="B78" s="47" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C78" s="45" t="inlineStr">
+      <c r="C78" s="47" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D78" s="46">
-        <f>'HOLERITE AGO.26'!D33</f>
-        <v/>
-      </c>
-      <c r="E78" s="47" t="n"/>
+      <c r="D78" s="48">
+        <f>'HOLERITE AGO.26'!D36</f>
+        <v/>
+      </c>
+      <c r="E78" s="49" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
@@ -5242,7 +5410,7 @@
         <f>'HOLERITE AGO.26'!E6</f>
         <v/>
       </c>
-      <c r="E80" s="41" t="n"/>
+      <c r="E80" s="43" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
@@ -5264,7 +5432,7 @@
         <f>'HOLERITE AGO.26'!E7</f>
         <v/>
       </c>
-      <c r="E81" s="41" t="n"/>
+      <c r="E81" s="43" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
@@ -5286,7 +5454,7 @@
         <f>'HOLERITE AGO.26'!E8</f>
         <v/>
       </c>
-      <c r="E82" s="41" t="n"/>
+      <c r="E82" s="43" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
@@ -5308,7 +5476,7 @@
         <f>'HOLERITE AGO.26'!E11</f>
         <v/>
       </c>
-      <c r="E83" s="41" t="n"/>
+      <c r="E83" s="43" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
@@ -5330,7 +5498,7 @@
         <f>'HOLERITE AGO.26'!E12</f>
         <v/>
       </c>
-      <c r="E84" s="41" t="n"/>
+      <c r="E84" s="43" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="29" t="inlineStr">
@@ -5349,10 +5517,10 @@
         </is>
       </c>
       <c r="D85" s="33">
-        <f>'HOLERITE AGO.26'!E13</f>
-        <v/>
-      </c>
-      <c r="E85" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E16</f>
+        <v/>
+      </c>
+      <c r="E85" s="43" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
@@ -5371,10 +5539,10 @@
         </is>
       </c>
       <c r="D86" s="33">
-        <f>'HOLERITE AGO.26'!E14</f>
-        <v/>
-      </c>
-      <c r="E86" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E17</f>
+        <v/>
+      </c>
+      <c r="E86" s="43" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
@@ -5393,10 +5561,10 @@
         </is>
       </c>
       <c r="D87" s="33">
-        <f>'HOLERITE AGO.26'!E15</f>
-        <v/>
-      </c>
-      <c r="E87" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E18</f>
+        <v/>
+      </c>
+      <c r="E87" s="43" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
@@ -5415,10 +5583,10 @@
         </is>
       </c>
       <c r="D88" s="33">
-        <f>'HOLERITE AGO.26'!E16</f>
-        <v/>
-      </c>
-      <c r="E88" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E88" s="43" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
@@ -5437,10 +5605,10 @@
         </is>
       </c>
       <c r="D89" s="33">
-        <f>'HOLERITE AGO.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E89" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E89" s="43" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="29" t="inlineStr">
@@ -5459,10 +5627,10 @@
         </is>
       </c>
       <c r="D90" s="33">
-        <f>'HOLERITE AGO.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E90" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E90" s="43" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="29" t="inlineStr">
@@ -5481,10 +5649,10 @@
         </is>
       </c>
       <c r="D91" s="33">
-        <f>'HOLERITE AGO.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E91" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E22</f>
+        <v/>
+      </c>
+      <c r="E91" s="43" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="29" t="inlineStr">
@@ -5503,10 +5671,10 @@
         </is>
       </c>
       <c r="D92" s="33">
-        <f>'HOLERITE AGO.26'!E20</f>
-        <v/>
-      </c>
-      <c r="E92" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E23</f>
+        <v/>
+      </c>
+      <c r="E92" s="43" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
@@ -5525,29 +5693,29 @@
         </is>
       </c>
       <c r="D93" s="33">
-        <f>'HOLERITE AGO.26'!E21</f>
-        <v/>
-      </c>
-      <c r="E93" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E24</f>
+        <v/>
+      </c>
+      <c r="E93" s="43" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="42" t="inlineStr">
+      <c r="A94" s="44" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B94" s="42" t="inlineStr">
+      <c r="B94" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C94" s="42" t="inlineStr">
+      <c r="C94" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D94" s="43">
-        <f>'HOLERITE AGO.26'!E22</f>
+      <c r="D94" s="45">
+        <f>'HOLERITE AGO.26'!E25</f>
         <v/>
       </c>
       <c r="E94" s="18" t="n"/>
@@ -5569,10 +5737,10 @@
         </is>
       </c>
       <c r="D95" s="33">
-        <f>'HOLERITE AGO.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E95" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E95" s="43" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="29" t="inlineStr">
@@ -5591,10 +5759,10 @@
         </is>
       </c>
       <c r="D96" s="33">
-        <f>'HOLERITE AGO.26'!E25</f>
-        <v/>
-      </c>
-      <c r="E96" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E96" s="43" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="29" t="inlineStr">
@@ -5613,10 +5781,10 @@
         </is>
       </c>
       <c r="D97" s="33">
-        <f>'HOLERITE AGO.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E97" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E97" s="43" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="29" t="inlineStr">
@@ -5635,10 +5803,10 @@
         </is>
       </c>
       <c r="D98" s="33">
-        <f>'HOLERITE AGO.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E98" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E98" s="43" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="29" t="inlineStr">
@@ -5657,10 +5825,10 @@
         </is>
       </c>
       <c r="D99" s="33">
-        <f>'HOLERITE AGO.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E99" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E31</f>
+        <v/>
+      </c>
+      <c r="E99" s="43" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="29" t="inlineStr">
@@ -5679,10 +5847,10 @@
         </is>
       </c>
       <c r="D100" s="33">
-        <f>'HOLERITE AGO.26'!E29</f>
-        <v/>
-      </c>
-      <c r="E100" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E32</f>
+        <v/>
+      </c>
+      <c r="E100" s="43" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="29" t="inlineStr">
@@ -5701,54 +5869,54 @@
         </is>
       </c>
       <c r="D101" s="33">
-        <f>'HOLERITE AGO.26'!E30</f>
-        <v/>
-      </c>
-      <c r="E101" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!E33</f>
+        <v/>
+      </c>
+      <c r="E101" s="43" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="42" t="inlineStr">
+      <c r="A102" s="44" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B102" s="42" t="inlineStr">
+      <c r="B102" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C102" s="42" t="inlineStr">
+      <c r="C102" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="43">
-        <f>'HOLERITE AGO.26'!E31</f>
+      <c r="D102" s="45">
+        <f>'HOLERITE AGO.26'!E34</f>
         <v/>
       </c>
       <c r="E102" s="18" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="44" t="inlineStr">
+      <c r="A103" s="46" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B103" s="45" t="inlineStr">
+      <c r="B103" s="47" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C103" s="45" t="inlineStr">
+      <c r="C103" s="47" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D103" s="46">
-        <f>'HOLERITE AGO.26'!E33</f>
-        <v/>
-      </c>
-      <c r="E103" s="47" t="n"/>
+      <c r="D103" s="48">
+        <f>'HOLERITE AGO.26'!E36</f>
+        <v/>
+      </c>
+      <c r="E103" s="49" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="29" t="inlineStr">
@@ -5770,7 +5938,7 @@
         <f>'HOLERITE AGO.26'!F6</f>
         <v/>
       </c>
-      <c r="E105" s="41" t="n"/>
+      <c r="E105" s="43" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="29" t="inlineStr">
@@ -5792,7 +5960,7 @@
         <f>'HOLERITE AGO.26'!F7</f>
         <v/>
       </c>
-      <c r="E106" s="41" t="n"/>
+      <c r="E106" s="43" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="29" t="inlineStr">
@@ -5814,7 +5982,7 @@
         <f>'HOLERITE AGO.26'!F8</f>
         <v/>
       </c>
-      <c r="E107" s="41" t="n"/>
+      <c r="E107" s="43" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="29" t="inlineStr">
@@ -5836,7 +6004,7 @@
         <f>'HOLERITE AGO.26'!F11</f>
         <v/>
       </c>
-      <c r="E108" s="41" t="n"/>
+      <c r="E108" s="43" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="29" t="inlineStr">
@@ -5858,7 +6026,7 @@
         <f>'HOLERITE AGO.26'!F12</f>
         <v/>
       </c>
-      <c r="E109" s="41" t="n"/>
+      <c r="E109" s="43" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
@@ -5877,10 +6045,10 @@
         </is>
       </c>
       <c r="D110" s="33">
-        <f>'HOLERITE AGO.26'!F13</f>
-        <v/>
-      </c>
-      <c r="E110" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F16</f>
+        <v/>
+      </c>
+      <c r="E110" s="43" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="29" t="inlineStr">
@@ -5899,10 +6067,10 @@
         </is>
       </c>
       <c r="D111" s="33">
-        <f>'HOLERITE AGO.26'!F14</f>
-        <v/>
-      </c>
-      <c r="E111" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F17</f>
+        <v/>
+      </c>
+      <c r="E111" s="43" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
@@ -5921,10 +6089,10 @@
         </is>
       </c>
       <c r="D112" s="33">
-        <f>'HOLERITE AGO.26'!F15</f>
-        <v/>
-      </c>
-      <c r="E112" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F18</f>
+        <v/>
+      </c>
+      <c r="E112" s="43" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
@@ -5943,10 +6111,10 @@
         </is>
       </c>
       <c r="D113" s="33">
-        <f>'HOLERITE AGO.26'!F16</f>
-        <v/>
-      </c>
-      <c r="E113" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E113" s="43" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="29" t="inlineStr">
@@ -5965,10 +6133,10 @@
         </is>
       </c>
       <c r="D114" s="33">
-        <f>'HOLERITE AGO.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E114" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E114" s="43" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="29" t="inlineStr">
@@ -5987,10 +6155,10 @@
         </is>
       </c>
       <c r="D115" s="33">
-        <f>'HOLERITE AGO.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E115" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E115" s="43" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="29" t="inlineStr">
@@ -6009,10 +6177,10 @@
         </is>
       </c>
       <c r="D116" s="33">
-        <f>'HOLERITE AGO.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E116" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F22</f>
+        <v/>
+      </c>
+      <c r="E116" s="43" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="29" t="inlineStr">
@@ -6031,10 +6199,10 @@
         </is>
       </c>
       <c r="D117" s="33">
-        <f>'HOLERITE AGO.26'!F20</f>
-        <v/>
-      </c>
-      <c r="E117" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F23</f>
+        <v/>
+      </c>
+      <c r="E117" s="43" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="29" t="inlineStr">
@@ -6053,29 +6221,29 @@
         </is>
       </c>
       <c r="D118" s="33">
-        <f>'HOLERITE AGO.26'!F21</f>
-        <v/>
-      </c>
-      <c r="E118" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F24</f>
+        <v/>
+      </c>
+      <c r="E118" s="43" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="42" t="inlineStr">
+      <c r="A119" s="44" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B119" s="42" t="inlineStr">
+      <c r="B119" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C119" s="42" t="inlineStr">
+      <c r="C119" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D119" s="43">
-        <f>'HOLERITE AGO.26'!F22</f>
+      <c r="D119" s="45">
+        <f>'HOLERITE AGO.26'!F25</f>
         <v/>
       </c>
       <c r="E119" s="18" t="n"/>
@@ -6097,10 +6265,10 @@
         </is>
       </c>
       <c r="D120" s="33">
-        <f>'HOLERITE AGO.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E120" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E120" s="43" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="29" t="inlineStr">
@@ -6119,10 +6287,10 @@
         </is>
       </c>
       <c r="D121" s="33">
-        <f>'HOLERITE AGO.26'!F25</f>
-        <v/>
-      </c>
-      <c r="E121" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E121" s="43" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="29" t="inlineStr">
@@ -6141,10 +6309,10 @@
         </is>
       </c>
       <c r="D122" s="33">
-        <f>'HOLERITE AGO.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E122" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E122" s="43" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="29" t="inlineStr">
@@ -6163,10 +6331,10 @@
         </is>
       </c>
       <c r="D123" s="33">
-        <f>'HOLERITE AGO.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E123" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E123" s="43" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="29" t="inlineStr">
@@ -6185,10 +6353,10 @@
         </is>
       </c>
       <c r="D124" s="33">
-        <f>'HOLERITE AGO.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E124" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F31</f>
+        <v/>
+      </c>
+      <c r="E124" s="43" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="29" t="inlineStr">
@@ -6207,10 +6375,10 @@
         </is>
       </c>
       <c r="D125" s="33">
-        <f>'HOLERITE AGO.26'!F29</f>
-        <v/>
-      </c>
-      <c r="E125" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F32</f>
+        <v/>
+      </c>
+      <c r="E125" s="43" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="29" t="inlineStr">
@@ -6229,54 +6397,54 @@
         </is>
       </c>
       <c r="D126" s="33">
-        <f>'HOLERITE AGO.26'!F30</f>
-        <v/>
-      </c>
-      <c r="E126" s="41" t="n"/>
+        <f>'HOLERITE AGO.26'!F33</f>
+        <v/>
+      </c>
+      <c r="E126" s="43" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="42" t="inlineStr">
+      <c r="A127" s="44" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B127" s="42" t="inlineStr">
+      <c r="B127" s="44" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C127" s="42" t="inlineStr">
+      <c r="C127" s="44" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D127" s="43">
-        <f>'HOLERITE AGO.26'!F31</f>
+      <c r="D127" s="45">
+        <f>'HOLERITE AGO.26'!F34</f>
         <v/>
       </c>
       <c r="E127" s="18" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="44" t="inlineStr">
+      <c r="A128" s="46" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B128" s="45" t="inlineStr">
+      <c r="B128" s="47" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C128" s="45" t="inlineStr">
+      <c r="C128" s="47" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D128" s="46">
-        <f>'HOLERITE AGO.26'!F33</f>
-        <v/>
-      </c>
-      <c r="E128" s="47" t="n"/>
+      <c r="D128" s="48">
+        <f>'HOLERITE AGO.26'!F36</f>
+        <v/>
+      </c>
+      <c r="E128" s="49" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E128"/>
@@ -6318,17 +6486,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Escolha o colaborador:</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Troque o nome aqui e a tabela abaixo muda sozinha — é o relatório para mandar para cada um.</t>
         </is>
@@ -6405,7 +6573,7 @@
         </is>
       </c>
       <c r="C12" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$13:$F$13,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$16:$F$16,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6416,7 +6584,7 @@
         </is>
       </c>
       <c r="C13" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$14:$F$14,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6427,7 +6595,7 @@
         </is>
       </c>
       <c r="C14" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$15:$F$15,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6438,7 +6606,7 @@
         </is>
       </c>
       <c r="C15" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$16:$F$16,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6449,7 +6617,7 @@
         </is>
       </c>
       <c r="C16" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6460,7 +6628,7 @@
         </is>
       </c>
       <c r="C17" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6471,7 +6639,7 @@
         </is>
       </c>
       <c r="C18" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6482,7 +6650,7 @@
         </is>
       </c>
       <c r="C19" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$23:$F$23,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6493,7 +6661,7 @@
         </is>
       </c>
       <c r="C20" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6503,8 +6671,8 @@
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="43">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+      <c r="C21" s="45">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$25:$F$25,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6524,7 +6692,7 @@
         </is>
       </c>
       <c r="C23" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6535,7 +6703,7 @@
         </is>
       </c>
       <c r="C24" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$25:$F$25,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6546,7 +6714,7 @@
         </is>
       </c>
       <c r="C25" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$26:$F$26,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6557,7 +6725,7 @@
         </is>
       </c>
       <c r="C26" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6568,7 +6736,7 @@
         </is>
       </c>
       <c r="C27" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6579,7 +6747,7 @@
         </is>
       </c>
       <c r="C28" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$32:$F$32,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6590,7 +6758,7 @@
         </is>
       </c>
       <c r="C29" s="33">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6600,8 +6768,8 @@
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C30" s="43">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+      <c r="C30" s="45">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$34:$F$34,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -6615,18 +6783,18 @@
       <c r="D31" s="28" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="50" t="inlineStr">
+      <c r="B32" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/09/2026</t>
         </is>
       </c>
-      <c r="C32" s="51">
-        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+      <c r="C32" s="53">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$36:$F$36,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="52" t="inlineStr">
+      <c r="B34" s="54" t="inlineStr">
         <is>
           <t>Vendas do colaborador no mês (InovaFarma):</t>
         </is>
@@ -6688,28 +6856,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>Nesta loja a comissão paga é o DOBRO da apurada — por isso os dois valores são diferentes.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE AGO.26.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="38" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
         </is>
@@ -6842,7 +7010,7 @@
         <f>ROUND(C5*F5,2)</f>
         <v/>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="55" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
@@ -6854,10 +7022,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="n"/>
-      <c r="B6" s="54" t="n"/>
-      <c r="C6" s="54" t="n"/>
-      <c r="D6" s="54" t="n"/>
+      <c r="A6" s="56" t="n"/>
+      <c r="B6" s="56" t="n"/>
+      <c r="C6" s="56" t="n"/>
+      <c r="D6" s="56" t="n"/>
       <c r="E6" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6867,14 +7035,14 @@
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="54" t="n"/>
-      <c r="I6" s="54" t="n"/>
+      <c r="H6" s="56" t="n"/>
+      <c r="I6" s="56" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="n"/>
-      <c r="B7" s="54" t="n"/>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="54" t="n"/>
+      <c r="A7" s="56" t="n"/>
+      <c r="B7" s="56" t="n"/>
+      <c r="C7" s="56" t="n"/>
+      <c r="D7" s="56" t="n"/>
       <c r="E7" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A7,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6884,14 +7052,14 @@
         <f>ROUND(C7*F7,2)</f>
         <v/>
       </c>
-      <c r="H7" s="54" t="n"/>
-      <c r="I7" s="54" t="n"/>
+      <c r="H7" s="56" t="n"/>
+      <c r="I7" s="56" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="n"/>
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="54" t="n"/>
-      <c r="D8" s="54" t="n"/>
+      <c r="A8" s="56" t="n"/>
+      <c r="B8" s="56" t="n"/>
+      <c r="C8" s="56" t="n"/>
+      <c r="D8" s="56" t="n"/>
       <c r="E8" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A8,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6901,14 +7069,14 @@
         <f>ROUND(C8*F8,2)</f>
         <v/>
       </c>
-      <c r="H8" s="54" t="n"/>
-      <c r="I8" s="54" t="n"/>
+      <c r="H8" s="56" t="n"/>
+      <c r="I8" s="56" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="54" t="n"/>
-      <c r="B9" s="54" t="n"/>
-      <c r="C9" s="54" t="n"/>
-      <c r="D9" s="54" t="n"/>
+      <c r="A9" s="56" t="n"/>
+      <c r="B9" s="56" t="n"/>
+      <c r="C9" s="56" t="n"/>
+      <c r="D9" s="56" t="n"/>
       <c r="E9" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A9,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6918,14 +7086,14 @@
         <f>ROUND(C9*F9,2)</f>
         <v/>
       </c>
-      <c r="H9" s="54" t="n"/>
-      <c r="I9" s="54" t="n"/>
+      <c r="H9" s="56" t="n"/>
+      <c r="I9" s="56" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="n"/>
-      <c r="B10" s="54" t="n"/>
-      <c r="C10" s="54" t="n"/>
-      <c r="D10" s="54" t="n"/>
+      <c r="A10" s="56" t="n"/>
+      <c r="B10" s="56" t="n"/>
+      <c r="C10" s="56" t="n"/>
+      <c r="D10" s="56" t="n"/>
       <c r="E10" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A10,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6935,14 +7103,14 @@
         <f>ROUND(C10*F10,2)</f>
         <v/>
       </c>
-      <c r="H10" s="54" t="n"/>
-      <c r="I10" s="54" t="n"/>
+      <c r="H10" s="56" t="n"/>
+      <c r="I10" s="56" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="n"/>
-      <c r="B11" s="54" t="n"/>
-      <c r="C11" s="54" t="n"/>
-      <c r="D11" s="54" t="n"/>
+      <c r="A11" s="56" t="n"/>
+      <c r="B11" s="56" t="n"/>
+      <c r="C11" s="56" t="n"/>
+      <c r="D11" s="56" t="n"/>
       <c r="E11" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A11,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6952,14 +7120,14 @@
         <f>ROUND(C11*F11,2)</f>
         <v/>
       </c>
-      <c r="H11" s="54" t="n"/>
-      <c r="I11" s="54" t="n"/>
+      <c r="H11" s="56" t="n"/>
+      <c r="I11" s="56" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="n"/>
-      <c r="B12" s="54" t="n"/>
-      <c r="C12" s="54" t="n"/>
-      <c r="D12" s="54" t="n"/>
+      <c r="A12" s="56" t="n"/>
+      <c r="B12" s="56" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
       <c r="E12" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A12,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6969,14 +7137,14 @@
         <f>ROUND(C12*F12,2)</f>
         <v/>
       </c>
-      <c r="H12" s="54" t="n"/>
-      <c r="I12" s="54" t="n"/>
+      <c r="H12" s="56" t="n"/>
+      <c r="I12" s="56" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="n"/>
-      <c r="B13" s="54" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="54" t="n"/>
+      <c r="A13" s="56" t="n"/>
+      <c r="B13" s="56" t="n"/>
+      <c r="C13" s="56" t="n"/>
+      <c r="D13" s="56" t="n"/>
       <c r="E13" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A13,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
@@ -6986,8 +7154,8 @@
         <f>ROUND(C13*F13,2)</f>
         <v/>
       </c>
-      <c r="H13" s="54" t="n"/>
-      <c r="I13" s="54" t="n"/>
+      <c r="H13" s="56" t="n"/>
+      <c r="I13" s="56" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
@@ -7056,7 +7224,7 @@
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="57" t="inlineStr">
         <is>
           <t>Atestado médico de 7 dias, entregue em 02/09/2026 — cobre de 02/09 a 08/09/2026.</t>
         </is>
